--- a/data/sources/countries/honduras.xlsx
+++ b/data/sources/countries/honduras.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI81"/>
+  <dimension ref="A1:BE82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +728,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -839,7 +743,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t xml:space="preserve"> Sinohydro Corporation Limited (PowerChina)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -896,15 +800,15 @@
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://spanish.news.cn/20230503/7b16052195c142e29d8d19fa8b8b49f7/c.html</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://spanish.news.cn/20230503/7b16052195c142e29d8d19fa8b8b49f7/c.html</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://www.laprensa.hn/honduras/honduras-hidroelectrica-sinohydro-avance-poderosa-china-continental-rio_patuca-FCLP1163798</t>
         </is>
@@ -934,7 +838,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -949,7 +853,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t xml:space="preserve"> Sinohydro Corporation Limited (PowerChina) — contratista EPC; propietaria: Energías Limpias del Yaguala S.A. de C.V. (privada hondureña)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1006,15 +910,15 @@
       <c r="BA3" t="n">
         <v>4</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://lombardi.group/eng/projects/arenal-a-new-arch-dam-for-honduras-energy-security</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://lombardi.group/eng/projects/arenal-a-new-arch-dam-for-honduras-energy-security</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/company-profile/energias-limpias-del-yaguala-sa-de-cv-el-yaguala</t>
         </is>
@@ -1023,15 +927,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HND-0004</t>
+          <t>HND-0003</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.41178275387732, -88.55224307150368</t>
+          <t>15.641501695248834, -87.92880179920729</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1044,7 +948,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1055,20 +959,20 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Texhong International Group / Danasun Energy (capital chino-hongkonés)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1082,12 +986,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Línea eléctrica de 197 km adjudicada por ENEE al consorcio Sinohydro–Equipos Industriales</t>
+          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión...</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>197 km power transmission line awarded by ENEE to the Sinohydro–Equipos Industriales consortium</t>
+          <t>Textile industrial park and a solar photovoltaic plant of over 300 MW on 400 hectares in Choloma</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1096,11 +1000,11 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>115</v>
+        <v>400</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Greenfield</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1116,32 +1020,32 @@
       <c r="BA4" t="n">
         <v>5</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://sreci.gob.hn/node/1460</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
+          <t>https://soydatos.hn/2026/02/13/texhong-invierte-400-millones-en-choloma-el-megaproyecto-chino-que-redefine-la-maquila-en-honduras/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HND-0004</t>
+          <t>HND-0003</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.35670354947725, -88.62476277732054</t>
+          <t>15.630540615343852, -87.92207960211847</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1154,7 +1058,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1165,20 +1069,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Texhong International Group / Danasun Energy (capital chino-hongkonés)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1192,12 +1096,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Línea eléctrica de 197 km adjudicada por ENEE al consorcio Sinohydro–Equipos Industriales</t>
+          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión...</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>197 km power transmission line awarded by ENEE to the Sinohydro–Equipos Industriales consortium</t>
+          <t>Textile industrial park and a solar photovoltaic plant of over 300 MW on 400 hectares in Choloma</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1206,11 +1110,11 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>115</v>
+        <v>400</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Greenfield</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1226,17 +1130,17 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://sreci.gob.hn/node/1460</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
+          <t>https://soydatos.hn/2026/02/13/texhong-invierte-400-millones-en-choloma-el-megaproyecto-chino-que-redefine-la-maquila-en-honduras/</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1155,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.32682853940727, -88.6761433139229</t>
+          <t>15.41178275387732, -88.55224307150368</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1264,7 +1168,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1279,7 +1183,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1288,7 +1192,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1336,15 +1240,15 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>0</v>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1361,7 +1265,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.28431195488705, -88.72463416892958</t>
+          <t>15.35670354947725, -88.62476277732054</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1374,7 +1278,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1389,7 +1293,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1398,7 +1302,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1446,15 +1350,15 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
-        <v>0</v>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1471,7 +1375,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.26559460181512, -88.76065624478443</t>
+          <t>15.32682853940727, -88.6761433139229</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1484,7 +1388,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1499,7 +1403,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1508,7 +1412,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1556,15 +1460,15 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>0</v>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1581,7 +1485,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.22011578831051, -88.77259452766516</t>
+          <t>15.28431195488705, -88.72463416892958</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1594,7 +1498,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1609,7 +1513,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1618,7 +1522,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1666,15 +1570,15 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>0</v>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1691,7 +1595,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.16307201490769, -88.83110607916896</t>
+          <t>15.26559460181512, -88.76065624478443</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1704,7 +1608,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1719,7 +1623,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1728,7 +1632,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1776,15 +1680,15 @@
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>0</v>
+      <c r="BB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1801,7 +1705,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.12057704578278, -88.85262699605686</t>
+          <t>15.22011578831051, -88.77259452766516</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1814,7 +1718,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1829,7 +1733,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1838,7 +1742,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1886,15 +1790,15 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>0</v>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -1911,7 +1815,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.06275975942378, -88.86161774924184</t>
+          <t>15.16307201490769, -88.83110607916896</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1924,7 +1828,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -1939,7 +1843,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1948,7 +1852,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1996,15 +1900,15 @@
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BC12" t="n">
-        <v>0</v>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2021,7 +1925,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.00564913181176, -88.83946721359955</t>
+          <t>15.12057704578278, -88.85262699605686</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2034,7 +1938,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -2049,7 +1953,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2058,7 +1962,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2106,15 +2010,15 @@
       <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="BC13" t="n">
-        <v>0</v>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2131,7 +2035,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.95565358444325, -88.82794141258759</t>
+          <t>15.06275975942378, -88.86161774924184</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2144,14 +2048,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HN-CO</t>
+          <t>HN-CR</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -2159,7 +2063,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2168,7 +2072,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2192,7 +2096,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>COPÁN</t>
+          <t>CORTÉS</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -2216,15 +2120,15 @@
       <c r="BA14" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>0</v>
+      <c r="BB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2241,7 +2145,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14.9182994804332, -88.84610300079771</t>
+          <t>15.00564913181176, -88.83946721359955</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2254,14 +2158,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HN-CO</t>
+          <t>HN-CR</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2269,7 +2173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2278,7 +2182,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2302,7 +2206,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>COPÁN</t>
+          <t>CORTÉS</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2326,15 +2230,15 @@
       <c r="BA15" t="n">
         <v>5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>0</v>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2351,7 +2255,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.85609472399249, -88.85851662985783</t>
+          <t>14.95565358444325, -88.82794141258759</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2364,7 +2268,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -2379,7 +2283,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2388,7 +2292,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2436,15 +2340,15 @@
       <c r="BA16" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
-        <v>0</v>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2461,7 +2365,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.786607, -86.395087</t>
+          <t>14.9182994804332, -88.84610300079771</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2474,14 +2378,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HN-OL</t>
+          <t>HN-CO</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2489,7 +2393,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2522,7 +2426,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>OLANCHO</t>
+          <t>COPÁN</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -2546,15 +2450,15 @@
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>0</v>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2571,7 +2475,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.80937989999996, -86.48009</t>
+          <t>14.85609472399249, -88.85851662985783</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2584,14 +2488,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>HN-OL</t>
+          <t>HN-CO</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2599,7 +2503,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2608,7 +2512,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2632,7 +2536,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>OLANCHO</t>
+          <t>COPÁN</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2656,15 +2560,15 @@
       <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>0</v>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2681,7 +2585,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.81493709999996, -86.5096656</t>
+          <t>15.786607, -86.395087</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2694,14 +2598,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HN-AT</t>
+          <t>HN-OL</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2709,7 +2613,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2718,7 +2622,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2742,7 +2646,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ATLÁNTIDA</t>
+          <t>OLANCHO</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2766,15 +2670,15 @@
       <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BC19" t="n">
-        <v>0</v>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2791,7 +2695,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15.78663915007976, -86.55207087873467</t>
+          <t>15.80937989999996, -86.48009</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2804,14 +2708,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HN-AT</t>
+          <t>HN-OL</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2819,7 +2723,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2828,7 +2732,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2852,7 +2756,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ATLÁNTIDA</t>
+          <t>OLANCHO</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2876,15 +2780,15 @@
       <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>0</v>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -2901,7 +2805,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.76807312409048, -86.58779318073915</t>
+          <t>15.81493709999996, -86.5096656</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2914,7 +2818,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -2929,7 +2833,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2938,7 +2842,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2986,15 +2890,15 @@
       <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="BC21" t="n">
-        <v>0</v>
+      <c r="BB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3011,7 +2915,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.7566579061139, -86.6593882965394</t>
+          <t>15.78663915007976, -86.55207087873467</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3024,7 +2928,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3039,7 +2943,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3048,7 +2952,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3096,15 +3000,15 @@
       <c r="BA22" t="n">
         <v>5</v>
       </c>
-      <c r="BC22" t="n">
-        <v>0</v>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3121,7 +3025,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.73556616841899, -86.73792252086655</t>
+          <t>15.76807312409048, -86.58779318073915</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3134,7 +3038,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3149,7 +3053,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3158,7 +3062,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3206,15 +3110,15 @@
       <c r="BA23" t="n">
         <v>5</v>
       </c>
-      <c r="BC23" t="n">
-        <v>0</v>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3231,7 +3135,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.70333280335753, -86.80575962918584</t>
+          <t>15.7566579061139, -86.6593882965394</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3244,7 +3148,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3259,7 +3163,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3268,7 +3172,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3316,15 +3220,15 @@
       <c r="BA24" t="n">
         <v>5</v>
       </c>
-      <c r="BC24" t="n">
-        <v>0</v>
+      <c r="BB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3341,7 +3245,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15.64123191923856, -86.84646169022257</t>
+          <t>15.73556616841899, -86.73792252086655</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3354,7 +3258,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3369,7 +3273,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3378,7 +3282,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3426,15 +3330,15 @@
       <c r="BA25" t="n">
         <v>5</v>
       </c>
-      <c r="BC25" t="n">
-        <v>0</v>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3451,7 +3355,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.58542429634853, -86.87522780504632</t>
+          <t>15.70333280335753, -86.80575962918584</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3464,7 +3368,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3479,7 +3383,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3488,7 +3392,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3536,15 +3440,15 @@
       <c r="BA26" t="n">
         <v>5</v>
       </c>
-      <c r="BC26" t="n">
-        <v>0</v>
+      <c r="BB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3561,7 +3465,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15.55735401753599, -86.91763761148307</t>
+          <t>15.64123191923856, -86.84646169022257</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3574,7 +3478,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3589,7 +3493,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3598,7 +3502,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3646,15 +3550,15 @@
       <c r="BA27" t="n">
         <v>5</v>
       </c>
-      <c r="BC27" t="n">
-        <v>0</v>
+      <c r="BB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3671,7 +3575,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15.52717801763281, -86.94666050612618</t>
+          <t>15.58542429634853, -86.87522780504632</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3684,7 +3588,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3699,7 +3603,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3708,7 +3612,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3756,15 +3660,15 @@
       <c r="BA28" t="n">
         <v>5</v>
       </c>
-      <c r="BC28" t="n">
-        <v>0</v>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3781,7 +3685,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15.48900531844916, -87.02600341496749</t>
+          <t>15.55735401753599, -86.91763761148307</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3794,7 +3698,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3809,7 +3713,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3818,7 +3722,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3866,15 +3770,15 @@
       <c r="BA29" t="n">
         <v>5</v>
       </c>
-      <c r="BC29" t="n">
-        <v>0</v>
+      <c r="BB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -3891,7 +3795,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.479754494647, -87.11072200295182</t>
+          <t>15.52717801763281, -86.94666050612618</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3904,7 +3808,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -3919,7 +3823,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3928,7 +3832,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -3976,15 +3880,15 @@
       <c r="BA30" t="n">
         <v>5</v>
       </c>
-      <c r="BC30" t="n">
-        <v>0</v>
+      <c r="BB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4001,7 +3905,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15.40908752185491, -87.12766456353785</t>
+          <t>15.48900531844916, -87.02600341496749</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4014,7 +3918,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4029,7 +3933,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4038,7 +3942,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4086,15 +3990,15 @@
       <c r="BA31" t="n">
         <v>5</v>
       </c>
-      <c r="BC31" t="n">
-        <v>0</v>
+      <c r="BB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4111,7 +4015,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.40317205163642, -87.19134845644041</t>
+          <t>15.479754494647, -87.11072200295182</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4124,7 +4028,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4139,7 +4043,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4148,7 +4052,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4196,15 +4100,15 @@
       <c r="BA32" t="n">
         <v>5</v>
       </c>
-      <c r="BC32" t="n">
-        <v>0</v>
+      <c r="BB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4221,7 +4125,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15.78280029999997, -86.8023595</t>
+          <t>15.40908752185491, -87.12766456353785</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4234,7 +4138,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4249,7 +4153,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4306,15 +4210,15 @@
       <c r="BA33" t="n">
         <v>5</v>
       </c>
-      <c r="BC33" t="n">
-        <v>0</v>
+      <c r="BB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4331,7 +4235,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15.75066944468452, -86.79052507493121</t>
+          <t>15.40317205163642, -87.19134845644041</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4344,7 +4248,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4359,7 +4263,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4368,7 +4272,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4416,15 +4320,15 @@
       <c r="BA34" t="n">
         <v>5</v>
       </c>
-      <c r="BC34" t="n">
-        <v>0</v>
+      <c r="BB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4441,7 +4345,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15.724673610499, -86.77711971979959</t>
+          <t>15.78280029999997, -86.8023595</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4454,7 +4358,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4469,7 +4373,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4478,7 +4382,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -4526,15 +4430,15 @@
       <c r="BA35" t="n">
         <v>5</v>
       </c>
-      <c r="BC35" t="n">
-        <v>0</v>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4551,7 +4455,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14.32942178086754, -88.4694818136123</t>
+          <t>15.75066944468452, -86.79052507493121</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4564,7 +4468,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -4579,7 +4483,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4612,7 +4516,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>INTIBUCÁ</t>
+          <t>ATLÁNTIDA</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -4636,15 +4540,15 @@
       <c r="BA36" t="n">
         <v>5</v>
       </c>
-      <c r="BC36" t="n">
-        <v>0</v>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4661,7 +4565,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14.34280781485911, -88.31818071189181</t>
+          <t>15.724673610499, -86.77711971979959</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4674,14 +4578,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HN-IN</t>
+          <t>HN-AT</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -4689,7 +4593,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4698,7 +4602,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -4722,7 +4626,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>INTIBUCÁ</t>
+          <t>ATLÁNTIDA</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -4746,15 +4650,15 @@
       <c r="BA37" t="n">
         <v>5</v>
       </c>
-      <c r="BC37" t="n">
-        <v>0</v>
+      <c r="BB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4771,7 +4675,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>14.38082268709208, -88.2069910312816</t>
+          <t>14.32942178086754, -88.4694818136123</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4784,14 +4688,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HN-IN</t>
+          <t>HN-AT</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -4799,7 +4703,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4808,7 +4712,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -4832,7 +4736,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>COMAYAGUA</t>
+          <t>INTIBUCÁ</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -4856,15 +4760,15 @@
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BC38" t="n">
-        <v>0</v>
+      <c r="BB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4881,7 +4785,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>14.40195655275153, -88.1385360199046</t>
+          <t>14.34280781485911, -88.31818071189181</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4894,14 +4798,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HN-CM</t>
+          <t>HN-IN</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -4909,7 +4813,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4918,7 +4822,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -4942,7 +4846,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>COMAYAGUA</t>
+          <t>INTIBUCÁ</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -4966,15 +4870,15 @@
       <c r="BA39" t="n">
         <v>5</v>
       </c>
-      <c r="BC39" t="n">
-        <v>0</v>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -4991,7 +4895,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>14.37311637281547, -88.09008944879619</t>
+          <t>14.38082268709208, -88.2069910312816</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5004,14 +4908,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HN-CM</t>
+          <t>HN-IN</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -5019,7 +4923,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5028,7 +4932,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -5076,15 +4980,15 @@
       <c r="BA40" t="n">
         <v>5</v>
       </c>
-      <c r="BC40" t="n">
-        <v>0</v>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5101,7 +5005,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14.36115354874944, -87.99055271860598</t>
+          <t>14.40195655275153, -88.1385360199046</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5114,7 +5018,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -5129,7 +5033,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5138,7 +5042,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -5186,15 +5090,15 @@
       <c r="BA41" t="n">
         <v>5</v>
       </c>
-      <c r="BC41" t="n">
-        <v>0</v>
+      <c r="BB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5211,7 +5115,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14.38634791761132, -87.92671311854461</t>
+          <t>14.37311637281547, -88.09008944879619</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5224,7 +5128,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -5239,7 +5143,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5248,7 +5152,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -5296,15 +5200,15 @@
       <c r="BA42" t="n">
         <v>5</v>
       </c>
-      <c r="BC42" t="n">
-        <v>0</v>
+      <c r="BB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5321,7 +5225,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14.42838667883665, -87.80313506083604</t>
+          <t>14.36115354874944, -87.99055271860598</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5334,7 +5238,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -5349,7 +5253,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5358,7 +5262,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -5406,15 +5310,15 @@
       <c r="BA43" t="n">
         <v>5</v>
       </c>
-      <c r="BC43" t="n">
-        <v>0</v>
+      <c r="BB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5431,7 +5335,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14.46614165151739, -87.70527197364413</t>
+          <t>14.38634791761132, -87.92671311854461</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5444,7 +5348,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -5459,7 +5363,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5468,7 +5372,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -5516,15 +5420,15 @@
       <c r="BA44" t="n">
         <v>5</v>
       </c>
-      <c r="BC44" t="n">
-        <v>0</v>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5541,7 +5445,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.55489154488413, -86.86225522018272</t>
+          <t>14.42838667883665, -87.80313506083604</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,14 +5458,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HN-CH</t>
+          <t>HN-CM</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5569,7 +5473,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5602,7 +5506,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CHOLUTECA</t>
+          <t>COMAYAGUA</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -5626,15 +5530,15 @@
       <c r="BA45" t="n">
         <v>5</v>
       </c>
-      <c r="BC45" t="n">
-        <v>0</v>
+      <c r="BB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5651,7 +5555,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.63590633529068, -86.90081801937059</t>
+          <t>14.46614165151739, -87.70527197364413</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5664,14 +5568,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HN-CH</t>
+          <t>HN-CM</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5679,7 +5583,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5688,7 +5592,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -5712,7 +5616,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CHOLUTECA</t>
+          <t>COMAYAGUA</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -5736,15 +5640,15 @@
       <c r="BA46" t="n">
         <v>5</v>
       </c>
-      <c r="BC46" t="n">
-        <v>0</v>
+      <c r="BB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5761,7 +5665,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.71315087182344, -86.8889285310737</t>
+          <t>13.55489154488413, -86.86225522018272</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5774,14 +5678,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HN-EP</t>
+          <t>HN-CH</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -5789,7 +5693,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5798,7 +5702,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -5822,7 +5726,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>EL PARAÍSO</t>
+          <t>CHOLUTECA</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -5846,15 +5750,15 @@
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="n">
-        <v>0</v>
+      <c r="BB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5871,7 +5775,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.81092628255706, -86.86456965312864</t>
+          <t>13.63590633529068, -86.90081801937059</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5884,14 +5788,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HN-EP</t>
+          <t>HN-CH</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5899,7 +5803,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5908,7 +5812,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -5932,7 +5836,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>EL PARAÍSO</t>
+          <t>CHOLUTECA</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -5956,15 +5860,15 @@
       <c r="BA48" t="n">
         <v>5</v>
       </c>
-      <c r="BC48" t="n">
-        <v>0</v>
+      <c r="BB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -5981,7 +5885,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13.88834874490429, -86.8948483236708</t>
+          <t>13.71315087182344, -86.8889285310737</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5994,7 +5898,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6009,7 +5913,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6018,7 +5922,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -6066,15 +5970,15 @@
       <c r="BA49" t="n">
         <v>5</v>
       </c>
-      <c r="BC49" t="n">
-        <v>0</v>
+      <c r="BB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6091,7 +5995,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13.94541065610418, -86.9461378594499</t>
+          <t>13.81092628255706, -86.86456965312864</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6104,7 +6008,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6119,7 +6023,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6128,7 +6032,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -6176,15 +6080,15 @@
       <c r="BA50" t="n">
         <v>5</v>
       </c>
-      <c r="BC50" t="n">
-        <v>0</v>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6201,7 +6105,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13.94105994070511, -87.03488045697975</t>
+          <t>13.88834874490429, -86.8948483236708</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6214,7 +6118,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6229,7 +6133,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6238,7 +6142,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -6286,15 +6190,15 @@
       <c r="BA51" t="n">
         <v>5</v>
       </c>
-      <c r="BC51" t="n">
-        <v>0</v>
+      <c r="BB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6311,7 +6215,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13.99425078801625, -87.0355407085932</t>
+          <t>13.94541065610418, -86.9461378594499</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6324,7 +6228,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6339,7 +6243,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6348,7 +6252,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -6396,15 +6300,15 @@
       <c r="BA52" t="n">
         <v>5</v>
       </c>
-      <c r="BC52" t="n">
-        <v>0</v>
+      <c r="BB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6421,7 +6325,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14.09678220487307, -87.01987553251685</t>
+          <t>13.94105994070511, -87.03488045697975</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6434,7 +6338,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6449,7 +6353,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6458,7 +6362,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -6506,15 +6410,15 @@
       <c r="BA53" t="n">
         <v>5</v>
       </c>
-      <c r="BC53" t="n">
-        <v>0</v>
+      <c r="BB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6531,7 +6435,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14.19126700486824, -87.03380790469441</t>
+          <t>13.99425078801625, -87.0355407085932</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6544,7 +6448,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6559,7 +6463,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6568,7 +6472,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -6616,15 +6520,15 @@
       <c r="BA54" t="n">
         <v>5</v>
       </c>
-      <c r="BC54" t="n">
-        <v>0</v>
+      <c r="BB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6641,7 +6545,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14.24036102051354, -87.15351585314349</t>
+          <t>14.09678220487307, -87.01987553251685</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6654,7 +6558,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6669,7 +6573,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6678,7 +6582,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -6726,15 +6630,15 @@
       <c r="BA55" t="n">
         <v>5</v>
       </c>
-      <c r="BC55" t="n">
-        <v>0</v>
+      <c r="BB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6751,7 +6655,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14.17891426379843, -87.03789410389894</t>
+          <t>14.19126700486824, -87.03380790469441</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6764,7 +6668,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6779,7 +6683,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6836,15 +6740,15 @@
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BC56" t="n">
-        <v>0</v>
+      <c r="BB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6861,7 +6765,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14.20371706032203, -86.99149748668702</t>
+          <t>14.24036102051354, -87.15351585314349</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6874,7 +6778,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6889,7 +6793,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6898,7 +6802,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -6946,15 +6850,15 @@
       <c r="BA57" t="n">
         <v>5</v>
       </c>
-      <c r="BC57" t="n">
-        <v>0</v>
+      <c r="BB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -6971,7 +6875,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>14.26572292528283, -86.88602192283616</t>
+          <t>14.17891426379843, -87.03789410389894</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6984,7 +6888,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -6999,7 +6903,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7008,7 +6912,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -7056,15 +6960,15 @@
       <c r="BA58" t="n">
         <v>5</v>
       </c>
-      <c r="BC58" t="n">
-        <v>0</v>
+      <c r="BB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7081,7 +6985,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14.27011489176048, -86.72469035315493</t>
+          <t>14.20371706032203, -86.99149748668702</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7094,7 +6998,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7109,7 +7013,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7118,7 +7022,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -7166,15 +7070,15 @@
       <c r="BA59" t="n">
         <v>5</v>
       </c>
-      <c r="BC59" t="n">
-        <v>0</v>
+      <c r="BB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG59" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7191,7 +7095,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>14.23727076888533, -86.64383547932859</t>
+          <t>14.26572292528283, -86.88602192283616</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7204,7 +7108,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7219,7 +7123,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7228,7 +7132,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -7276,15 +7180,15 @@
       <c r="BA60" t="n">
         <v>5</v>
       </c>
-      <c r="BC60" t="n">
-        <v>0</v>
+      <c r="BB60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7301,7 +7205,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14.23322108567361, -86.58443963156621</t>
+          <t>14.27011489176048, -86.72469035315493</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7314,7 +7218,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7329,7 +7233,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7338,7 +7242,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -7386,15 +7290,15 @@
       <c r="BA61" t="n">
         <v>5</v>
       </c>
-      <c r="BC61" t="n">
-        <v>0</v>
+      <c r="BB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7411,7 +7315,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14.27454494781644, -86.38102758457211</t>
+          <t>14.23727076888533, -86.64383547932859</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7424,7 +7328,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7439,7 +7343,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7448,7 +7352,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -7496,15 +7400,15 @@
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BC62" t="n">
-        <v>0</v>
+      <c r="BB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7521,7 +7425,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>14.30341046343454, -86.33864433427033</t>
+          <t>14.23322108567361, -86.58443963156621</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7534,7 +7438,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7549,7 +7453,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7558,7 +7462,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -7606,15 +7510,15 @@
       <c r="BA63" t="n">
         <v>5</v>
       </c>
-      <c r="BC63" t="n">
-        <v>0</v>
+      <c r="BB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7631,7 +7535,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14.35706254342533, -86.27923927391929</t>
+          <t>14.27454494781644, -86.38102758457211</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7644,7 +7548,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7659,7 +7563,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7668,7 +7572,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -7716,15 +7620,15 @@
       <c r="BA64" t="n">
         <v>5</v>
       </c>
-      <c r="BC64" t="n">
-        <v>0</v>
+      <c r="BB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7741,7 +7645,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14.46458370664412, -86.17711203358625</t>
+          <t>14.30341046343454, -86.33864433427033</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7754,7 +7658,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7769,7 +7673,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -7778,7 +7682,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -7826,15 +7730,15 @@
       <c r="BA65" t="n">
         <v>5</v>
       </c>
-      <c r="BC65" t="n">
-        <v>0</v>
+      <c r="BB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7851,7 +7755,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14.60568017715797, -86.07872090145861</t>
+          <t>14.35706254342533, -86.27923927391929</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7864,7 +7768,7 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
@@ -7879,7 +7783,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -7888,7 +7792,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -7912,7 +7816,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>OLANCHO</t>
+          <t>EL PARAÍSO</t>
         </is>
       </c>
       <c r="R66" t="n">
@@ -7936,15 +7840,15 @@
       <c r="BA66" t="n">
         <v>5</v>
       </c>
-      <c r="BC66" t="n">
-        <v>0</v>
+      <c r="BB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -7961,7 +7865,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14.66395732123546, -86.05714972907238</t>
+          <t>14.46458370664412, -86.17711203358625</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7974,14 +7878,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>HN-OL</t>
+          <t>HN-EP</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -7989,7 +7893,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7998,7 +7902,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -8022,7 +7926,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>OLANCHO</t>
+          <t>EL PARAÍSO</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -8046,15 +7950,15 @@
       <c r="BA67" t="n">
         <v>5</v>
       </c>
-      <c r="BC67" t="n">
-        <v>0</v>
+      <c r="BB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8071,7 +7975,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15.13314257495967, -88.30513362208707</t>
+          <t>14.60568017715797, -86.07872090145861</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8084,14 +7988,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>HN-OL</t>
+          <t>HN-EP</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -8099,7 +8003,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8132,7 +8036,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CORTÉS</t>
+          <t>OLANCHO</t>
         </is>
       </c>
       <c r="R68" t="n">
@@ -8156,15 +8060,15 @@
       <c r="BA68" t="n">
         <v>5</v>
       </c>
-      <c r="BC68" t="n">
-        <v>0</v>
+      <c r="BB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8181,7 +8085,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15.10759373066058, -88.31725941451553</t>
+          <t>14.66395732123546, -86.05714972907238</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8194,14 +8098,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HN-CR</t>
+          <t>HN-OL</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -8209,7 +8113,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8218,7 +8122,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -8242,7 +8146,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>CORTÉS</t>
+          <t>OLANCHO</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -8266,15 +8170,15 @@
       <c r="BA69" t="n">
         <v>5</v>
       </c>
-      <c r="BC69" t="n">
-        <v>0</v>
+      <c r="BB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG69" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8291,7 +8195,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15.06505370140019, -88.33745879464591</t>
+          <t>15.13314257495967, -88.30513362208707</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8304,14 +8208,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>HN-CR</t>
+          <t>HN-OL</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -8319,7 +8223,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8328,7 +8232,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -8376,15 +8280,15 @@
       <c r="BA70" t="n">
         <v>5</v>
       </c>
-      <c r="BC70" t="n">
-        <v>0</v>
+      <c r="BB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8401,7 +8305,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14.90831695178042, -88.3179309823655</t>
+          <t>15.10759373066058, -88.31725941451553</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8414,14 +8318,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>HN-SB</t>
+          <t>HN-CR</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -8429,7 +8333,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8438,7 +8342,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -8462,7 +8366,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>SANTA BÁRBARA</t>
+          <t>CORTÉS</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -8486,15 +8390,15 @@
       <c r="BA71" t="n">
         <v>5</v>
       </c>
-      <c r="BC71" t="n">
-        <v>0</v>
+      <c r="BB71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8511,7 +8415,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14.91280930906046, -88.20008350336222</t>
+          <t>15.06505370140019, -88.33745879464591</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8524,14 +8428,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>HN-IN</t>
+          <t>HN-CR</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -8539,7 +8443,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8548,7 +8452,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -8572,7 +8476,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>INTIBUCÁ</t>
+          <t>CORTÉS</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -8596,15 +8500,15 @@
       <c r="BA72" t="n">
         <v>5</v>
       </c>
-      <c r="BC72" t="n">
-        <v>0</v>
+      <c r="BB72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8621,7 +8525,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14.81187049484361, -88.10487423245286</t>
+          <t>14.90831695178042, -88.3179309823655</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8634,14 +8538,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>HN-CM</t>
+          <t>HN-SB</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -8649,7 +8553,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8658,7 +8562,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -8682,7 +8586,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>COMAYAGUA</t>
+          <t>SANTA BÁRBARA</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -8706,15 +8610,15 @@
       <c r="BA73" t="n">
         <v>5</v>
       </c>
-      <c r="BC73" t="n">
-        <v>0</v>
+      <c r="BB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG73" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8731,7 +8635,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14.83307483338753, -88.04036595146063</t>
+          <t>14.91280930906046, -88.20008350336222</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8744,14 +8648,14 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>HN-CM</t>
+          <t>HN-IN</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -8759,7 +8663,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sinohydro</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -8768,7 +8672,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -8792,7 +8696,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>COMAYAGUA</t>
+          <t>INTIBUCÁ</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -8816,15 +8720,15 @@
       <c r="BA74" t="n">
         <v>5</v>
       </c>
-      <c r="BC74" t="n">
-        <v>0</v>
+      <c r="BB74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
-        </is>
-      </c>
-      <c r="BG74" t="inlineStr">
         <is>
           <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
@@ -8833,135 +8737,125 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HND-0005</t>
+          <t>HND-0004</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>14.81187049484361, -88.10487423245286</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>HN-CM</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Línea eléctrica de 197 km adjudicada por ENEE al consorcio Sinohydro–Equipos Industriales</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>197 km power transmission line awarded by ENEE to the Sinohydro–Equipos Industriales consortium</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>COMAYAGUA</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>115</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA75" t="n">
         <v>5</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>15.607134717982753, -87.9702598070611</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Honduras</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>HND</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>HN-CR</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Sunda International</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Manufactura</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Complejo quimico, de panales y de ceramica de Sunda International Group Monto</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Sunda International Group complex for chemicals, nappies, ceramics, sanitary ware, hardware and personal care products</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>CORTÉS</t>
-        </is>
-      </c>
-      <c r="R75" t="n">
-        <v>500</v>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Greenfield</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BA75" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD75" t="inlineStr">
-        <is>
-          <t>anuncio no ejecutado</t>
+      <c r="BB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>https://gobiernosolidario.sgjd.gob.hn/8969/empresa-china-sunda-international-group-invierte-en-honduras-y-creara-mas-de-3300-empleos/</t>
-        </is>
-      </c>
-      <c r="BF75" t="inlineStr">
-        <is>
-          <t>https://www.laprensa.hn/honduras/honduras-economia-empresa-china-invierte-pais-empleos-convenio-CB16174969</t>
-        </is>
-      </c>
-      <c r="BG75" t="inlineStr">
-        <is>
-          <t>https://www.elheraldo.hn/honduras/empresa-china-creara-mas-tres-mil-empleos-honduras-OB16175182</t>
+          <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HND-0006</t>
+          <t>HND-0004</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>14.0723, -87.1921</t>
+          <t>14.83307483338753, -88.04036595146063</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8974,31 +8868,31 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>HN-FM</t>
+          <t>HN-CM</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>GEIDCO</t>
+          <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Punto</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9007,27 +8901,30 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Carta de intencion GEIDCO-Gobierno de Honduras</t>
+          <t>Línea eléctrica de 197 km adjudicada por ENEE al consorcio Sinohydro–Equipos Industriales</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Letter of Intent between GEIDCO and the Government of Honduras</t>
+          <t>197 km power transmission line awarded by ENEE to the Sinohydro–Equipos Industriales consortium</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>FRANCISCO MORAZÁN</t>
-        </is>
+          <t>COMAYAGUA</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>115</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Greenfield</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9041,34 +8938,34 @@
         </is>
       </c>
       <c r="BA76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD76" t="inlineStr">
-        <is>
-          <t>fuera de alcance</t>
+        <v>5</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>https://www.latribuna.hn/2024/12/24/enee-anuncia-adjudicacion-de-proyecto-energetico-mas-importante/</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>https://www.laprensa.hn/opinion/columnas/hacia-donde-va-la-relacion-entre-china-y-honduras-KE30520309</t>
+          <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HND-0007</t>
+          <t>HND-0005</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>14.24496480412851, -87.33880950361853</t>
+          <t>15.607134717982753, -87.9702598070611</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9081,22 +8978,22 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>HN-FM</t>
+          <t>HN-CR</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>Sunda International Group</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9109,27 +9006,27 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Manufactura</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Represa de la microcuenca del Rio del Hombre, valle de Amarateca</t>
+          <t>Complejo quimico, de panales y de ceramica de Sunda International Group Monto</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Dam on the Rio del Hombre micro-basin in the Amarateca valley, under a letter of understanding signed on 12 September 2024 between CCECC and the mayor of Tegucigalpa, who valued it at USD 500-550M without specifying financing.</t>
+          <t>Sunda International Group complex for chemicals, nappies, ceramics, sanitary ware, hardware and personal care products</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>FRANCISCO MORAZÁN</t>
+          <t>CORTÉS</t>
         </is>
       </c>
       <c r="R77" t="n">
@@ -9137,7 +9034,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Greenfield</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9153,37 +9050,37 @@
       <c r="BA77" t="n">
         <v>3</v>
       </c>
-      <c r="BC77" t="n">
-        <v>1</v>
+      <c r="BB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>https://gobiernosolidario.sgjd.gob.hn/8969/empresa-china-sunda-international-group-invierte-en-honduras-y-creara-mas-de-3300-empleos/</t>
+        </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>carta de entendimiento sin ejecucion</t>
+          <t>https://www.laprensa.hn/honduras/honduras-economia-empresa-china-invierte-pais-empleos-convenio-CB16174969</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>https://www.expedientepublico.org/empresa-china-acusada-de-sobornos-construira-una-represa-en-honduras/</t>
-        </is>
-      </c>
-      <c r="BF77" t="inlineStr">
-        <is>
-          <t>https://dialogo-americas.com/articles/corrupt-china-state-owned-company-to-build-dam-in-honduras/</t>
+          <t>https://www.elheraldo.hn/honduras/empresa-china-creara-mas-tres-mil-empleos-honduras-OB16175182</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HND-0008</t>
+          <t>HND-0006</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13.404889440793402, -87.42953439236595</t>
+          <t>14.0723, -87.1921</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9196,22 +9093,22 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HN-CH</t>
+          <t>HN-FM</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>GEIDCO (Global Energy Interconnection Development and Cooperation Organization)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9224,35 +9121,32 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Ampliacion de los puertos de San Lorenzo y Puerto Cortes</t>
+          <t>Carta de intencion GEIDCO-Gobierno de Honduras</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Expansion of the San Lorenzo and Puerto Cortes ports under a memorandum of understanding signed on 29 May 2023 between the National Port Authority and CHEC, structured in three phases and covered by a confidentiality clause.</t>
+          <t>Letter of Intent between GEIDCO and the Government of Honduras</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CHOLUTECA</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
-        <v>240</v>
+          <t>FRANCISCO MORAZÁN</t>
+        </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Greenfield</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9266,44 +9160,29 @@
         </is>
       </c>
       <c r="BA78" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD78" t="inlineStr">
-        <is>
-          <t>MoU sin ejecucion</t>
-        </is>
-      </c>
-      <c r="BE78" t="inlineStr">
-        <is>
-          <t>https://www.expedientepublico.org/empresa-portuaria-de-honduras-blinda-de-secretismo-acuerdo-con-empresa-china/</t>
-        </is>
-      </c>
-      <c r="BF78" t="inlineStr">
-        <is>
-          <t>https://www.eleconomista.net/economia/Puerto-de-San-Lorenzo-en-Honduras-sera-ampliado-por-una-empresa-china-20230818-0004.html</t>
-        </is>
-      </c>
-      <c r="BG78" t="inlineStr">
-        <is>
-          <t>https://www.vesselfinder.com/news/8306-OPC-and-China-Harbour-Engineering-Company-ink-deal-for-Puerto-Cortes-expansion</t>
+        <v>1</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>https://www.laprensa.hn/opinion/columnas/hacia-donde-va-la-relacion-entre-china-y-honduras-KE30520309</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HND-0009</t>
+          <t>HND-0007</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15.346289209775602, -88.18357746404959</t>
+          <t>14.24496480412851, -87.33880950361853</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9316,22 +9195,22 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>HN-CR</t>
+          <t>HN-FM</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Danasun Energy</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -9344,35 +9223,35 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Manufactura</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Parque industrial textil, planta solar de 300 MW y conexión vial a Puerto Cortés</t>
+          <t>Represa de la microcuenca del Rio del Hombre, valle de Amarateca</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Textile industrial park, 300 MW solar plant, and road connection to Puerto Cortés, Choloma</t>
+          <t>Dam on the Rio del Hombre micro-basin in the Amarateca valley, under a letter of understanding signed on 12 September 2024 between CCECC and the mayor of Tegucigalpa, who valued it at USD 500-550M without specifying financing.</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CORTÉS</t>
+          <t>FRANCISCO MORAZÁN</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Greenfield</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -9386,44 +9265,34 @@
         </is>
       </c>
       <c r="BA79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>https://www.expedientepublico.org/empresa-china-acusada-de-sobornos-construira-una-represa-en-honduras/</t>
+        </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>anuncio no ejecutado</t>
-        </is>
-      </c>
-      <c r="BE79" t="inlineStr">
-        <is>
-          <t>https://www.infobae.com/honduras/2026/02/12/empresa-de-hong-kong-invertira-usd-400-millones-en-honduras-para-desarrollar-parque-solar-complejo-industrial-y-conexion-directa-a-puerto-cortes/</t>
-        </is>
-      </c>
-      <c r="BF79" t="inlineStr">
-        <is>
-          <t>https://proceso.hn/honduras-asegura-millonaria-inversion-con-nuevo-parque-industrial-en-choloma-informa-gobierno/</t>
-        </is>
-      </c>
-      <c r="BG79" t="inlineStr">
-        <is>
-          <t>https://www.laprensa.hn/honduras/inversion-400-millones-dolares-parque-industrial-choloma-KM29256396</t>
+          <t>https://dialogo-americas.com/articles/corrupt-china-state-owned-company-to-build-dam-in-honduras/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HND-0010</t>
+          <t>HND-0008</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14.105988177859139, -87.20486558328662</t>
+          <t>13.404889440793402, -87.42953439236595</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9436,22 +9305,22 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HN-FM</t>
+          <t>HN-CH</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Unidentified</t>
+          <t>China Harbour Engineering Company (CHEC), filial de CCCC</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9469,26 +9338,26 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Centro de Convenciones de Tegucigalpa</t>
+          <t>Ampliacion de los puertos de San Lorenzo y Puerto Cortes</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tegucigalpa Convention Centre</t>
+          <t>Expansion of the San Lorenzo and Puerto Cortes ports under a memorandum of understanding signed on 29 May 2023 between the National Port Authority and CHEC, structured in three phases and covered by a confidentiality clause.</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>FRANCISCO MORAZÁN</t>
+          <t>CHOLUTECA</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -9506,34 +9375,39 @@
         </is>
       </c>
       <c r="BA80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC80" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>https://www.expedientepublico.org/empresa-portuaria-de-honduras-blinda-de-secretismo-acuerdo-con-empresa-china/</t>
+        </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>en estudio</t>
+          <t>https://www.eleconomista.net/economia/Puerto-de-San-Lorenzo-en-Honduras-sera-ampliado-por-una-empresa-china-20230818-0004.html</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>https://www.expedientepublico.org/honduras-esconde-informacion-de-proyecto-de-us80-millones-con-china/</t>
+          <t>https://www.vesselfinder.com/news/8306-OPC-and-China-Harbour-Engineering-Company-ink-deal-for-Puerto-Cortes-expansion</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HND-0011</t>
+          <t>HND-0009</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15.5042, -88.0250</t>
+          <t>15.346289209775602, -88.18357746404959</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9546,17 +9420,22 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="1" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>HN-CR</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>China Energy Engineering Group</t>
+          <t>Danasun Energy</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9569,73 +9448,171 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Manufactura</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Ampliacion de las centrales termicas La Puerta (San Pedro Sula) y Ceiba Termica para 80 MW de potencia firme. China Energy gano la licitacion de la ENEE como unico oferente el 2 de febrero de 2024; la ENEE rescindio por incumplimientos y la empresa demando al Estado por USD 127,4M.</t>
+          <t>Parque industrial textil, planta solar de 300 MW y conexión vial a Puerto Cortés</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Expansion of the La Puerta (San Pedro Sula) and Ceiba Termica power plants for 80 MW of firm capacity. China Energy won the ENEE tender as sole bidder on 2 February 2024; ENEE rescinded for non-performance and the company sued the state for USD 127.4M.</t>
+          <t>Textile industrial park, 300 MW solar plant, and road connection to Puerto Cortés, Choloma</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Cortes</t>
-        </is>
+          <t>CORTÉS</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>400</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
+          <t>Greenfield</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/honduras/2026/02/12/empresa-de-hong-kong-invertira-usd-400-millones-en-honduras-para-desarrollar-parque-solar-complejo-industrial-y-conexion-directa-a-puerto-cortes/</t>
+        </is>
+      </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>https://proceso.hn/honduras-asegura-millonaria-inversion-con-nuevo-parque-industrial-en-choloma-informa-gobierno/</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>https://www.laprensa.hn/honduras/inversion-400-millones-dolares-parque-industrial-choloma-KM29256396</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HND-0010</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>10</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>14.105988177859139, -87.20486558328662</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>HN-FM</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Por identificar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Centro de Convenciones de Tegucigalpa</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tegucigalpa Convention Centre</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>FRANCISCO MORAZÁN</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>80</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA81" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD81" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE81" t="inlineStr">
-        <is>
-          <t>https://www.expedientepublico.org/china-energy-gano-licitacion-sin-competidores-en-honduras/</t>
-        </is>
-      </c>
-      <c r="BF81" t="inlineStr">
-        <is>
-          <t>https://www.elheraldo.hn/honduras/empresa-china-demanda-estado-honduras-127-millones-NC21107930</t>
-        </is>
-      </c>
-      <c r="BG81" t="inlineStr">
-        <is>
-          <t>https://proceso.hn/china-se-estrena-en-honduras-con-millonaria-demanda-al-sector-electrico/</t>
-        </is>
-      </c>
-      <c r="BH81" t="inlineStr">
-        <is>
-          <t>https://www.latribuna.hn/2024/08/29/corte-admite-millonaria-demanda-contra-la-enee/</t>
+      <c r="BA82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>https://www.expedientepublico.org/honduras-esconde-informacion-de-proyecto-de-us80-millones-con-china/</t>
         </is>
       </c>
     </row>

--- a/data/sources/countries/honduras.xlsx
+++ b/data/sources/countries/honduras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESE_39\Downloads\Entrega ICLAC_IMFD-20260518T163702Z-3-001\países_finales_copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24534E0-C7E8-429D-85A3-D28AC3A279AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6063A30A-C9EB-4538-8603-BCFDF530500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="BB6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="s">
         <v>100</v>
@@ -1687,7 +1687,7 @@
         <v>5</v>
       </c>
       <c r="BB7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="s">
         <v>100</v>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="BB8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="s">
         <v>100</v>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="BB9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="s">
         <v>100</v>
@@ -1909,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="BB10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="s">
         <v>100</v>
@@ -1983,7 +1983,7 @@
         <v>5</v>
       </c>
       <c r="BB11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="s">
         <v>100</v>
@@ -2057,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="BB12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="s">
         <v>100</v>
@@ -2131,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="BB13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="s">
         <v>100</v>
@@ -2205,7 +2205,7 @@
         <v>5</v>
       </c>
       <c r="BB14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="s">
         <v>100</v>
@@ -2279,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="BB15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="s">
         <v>100</v>
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="BB16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="s">
         <v>100</v>
@@ -2427,7 +2427,7 @@
         <v>5</v>
       </c>
       <c r="BB17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="s">
         <v>100</v>
@@ -2501,7 +2501,7 @@
         <v>5</v>
       </c>
       <c r="BB18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="s">
         <v>100</v>
@@ -2575,7 +2575,7 @@
         <v>5</v>
       </c>
       <c r="BB19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="s">
         <v>100</v>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="BB20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="s">
         <v>100</v>
@@ -2723,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="BB21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="s">
         <v>100</v>
@@ -2797,7 +2797,7 @@
         <v>5</v>
       </c>
       <c r="BB22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="s">
         <v>100</v>
@@ -2871,7 +2871,7 @@
         <v>5</v>
       </c>
       <c r="BB23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="s">
         <v>100</v>
@@ -2945,7 +2945,7 @@
         <v>5</v>
       </c>
       <c r="BB24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="s">
         <v>100</v>
@@ -3019,7 +3019,7 @@
         <v>5</v>
       </c>
       <c r="BB25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="s">
         <v>100</v>
@@ -3093,7 +3093,7 @@
         <v>5</v>
       </c>
       <c r="BB26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="s">
         <v>100</v>
@@ -3167,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="BB27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="s">
         <v>100</v>
@@ -3241,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="BB28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="s">
         <v>100</v>
@@ -3315,7 +3315,7 @@
         <v>5</v>
       </c>
       <c r="BB29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="s">
         <v>100</v>
@@ -3389,7 +3389,7 @@
         <v>5</v>
       </c>
       <c r="BB30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="s">
         <v>100</v>
@@ -3463,7 +3463,7 @@
         <v>5</v>
       </c>
       <c r="BB31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="s">
         <v>100</v>
@@ -3537,7 +3537,7 @@
         <v>5</v>
       </c>
       <c r="BB32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="s">
         <v>100</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BB33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="s">
         <v>100</v>
@@ -3685,7 +3685,7 @@
         <v>5</v>
       </c>
       <c r="BB34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="s">
         <v>100</v>
@@ -3759,7 +3759,7 @@
         <v>5</v>
       </c>
       <c r="BB35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="s">
         <v>100</v>
@@ -3833,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="BB36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="s">
         <v>100</v>
@@ -3907,7 +3907,7 @@
         <v>5</v>
       </c>
       <c r="BB37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="s">
         <v>100</v>
@@ -3981,7 +3981,7 @@
         <v>5</v>
       </c>
       <c r="BB38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="s">
         <v>100</v>
@@ -4055,7 +4055,7 @@
         <v>5</v>
       </c>
       <c r="BB39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="s">
         <v>100</v>
@@ -4129,7 +4129,7 @@
         <v>5</v>
       </c>
       <c r="BB40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="s">
         <v>100</v>
@@ -4203,7 +4203,7 @@
         <v>5</v>
       </c>
       <c r="BB41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="s">
         <v>100</v>
@@ -4277,7 +4277,7 @@
         <v>5</v>
       </c>
       <c r="BB42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="s">
         <v>100</v>
@@ -4351,7 +4351,7 @@
         <v>5</v>
       </c>
       <c r="BB43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="s">
         <v>100</v>
@@ -4425,7 +4425,7 @@
         <v>5</v>
       </c>
       <c r="BB44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="s">
         <v>100</v>
@@ -4499,7 +4499,7 @@
         <v>5</v>
       </c>
       <c r="BB45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="s">
         <v>100</v>
@@ -4573,7 +4573,7 @@
         <v>5</v>
       </c>
       <c r="BB46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="s">
         <v>100</v>
@@ -4647,7 +4647,7 @@
         <v>5</v>
       </c>
       <c r="BB47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="s">
         <v>100</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="BB48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="s">
         <v>100</v>
@@ -4795,7 +4795,7 @@
         <v>5</v>
       </c>
       <c r="BB49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="s">
         <v>100</v>
@@ -4869,7 +4869,7 @@
         <v>5</v>
       </c>
       <c r="BB50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="s">
         <v>100</v>
@@ -4943,7 +4943,7 @@
         <v>5</v>
       </c>
       <c r="BB51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="s">
         <v>100</v>
@@ -5017,7 +5017,7 @@
         <v>5</v>
       </c>
       <c r="BB52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="s">
         <v>100</v>
@@ -5091,7 +5091,7 @@
         <v>5</v>
       </c>
       <c r="BB53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="s">
         <v>100</v>
@@ -5165,7 +5165,7 @@
         <v>5</v>
       </c>
       <c r="BB54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="s">
         <v>100</v>
@@ -5239,7 +5239,7 @@
         <v>5</v>
       </c>
       <c r="BB55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="s">
         <v>100</v>
@@ -5313,7 +5313,7 @@
         <v>5</v>
       </c>
       <c r="BB56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="s">
         <v>100</v>
@@ -5387,7 +5387,7 @@
         <v>5</v>
       </c>
       <c r="BB57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="s">
         <v>100</v>
@@ -5461,7 +5461,7 @@
         <v>5</v>
       </c>
       <c r="BB58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC58" t="s">
         <v>100</v>
@@ -5535,7 +5535,7 @@
         <v>5</v>
       </c>
       <c r="BB59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="s">
         <v>100</v>
@@ -5609,7 +5609,7 @@
         <v>5</v>
       </c>
       <c r="BB60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="s">
         <v>100</v>
@@ -5683,7 +5683,7 @@
         <v>5</v>
       </c>
       <c r="BB61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC61" t="s">
         <v>100</v>
@@ -5757,7 +5757,7 @@
         <v>5</v>
       </c>
       <c r="BB62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="s">
         <v>100</v>
@@ -5831,7 +5831,7 @@
         <v>5</v>
       </c>
       <c r="BB63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC63" t="s">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>5</v>
       </c>
       <c r="BB64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC64" t="s">
         <v>100</v>
@@ -5979,7 +5979,7 @@
         <v>5</v>
       </c>
       <c r="BB65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC65" t="s">
         <v>100</v>
@@ -6053,7 +6053,7 @@
         <v>5</v>
       </c>
       <c r="BB66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC66" t="s">
         <v>100</v>
@@ -6127,7 +6127,7 @@
         <v>5</v>
       </c>
       <c r="BB67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC67" t="s">
         <v>100</v>
@@ -6201,7 +6201,7 @@
         <v>5</v>
       </c>
       <c r="BB68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC68" t="s">
         <v>100</v>
@@ -6275,7 +6275,7 @@
         <v>5</v>
       </c>
       <c r="BB69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC69" t="s">
         <v>100</v>
@@ -6349,7 +6349,7 @@
         <v>5</v>
       </c>
       <c r="BB70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC70" t="s">
         <v>100</v>
@@ -6423,7 +6423,7 @@
         <v>5</v>
       </c>
       <c r="BB71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC71" t="s">
         <v>100</v>
@@ -6497,7 +6497,7 @@
         <v>5</v>
       </c>
       <c r="BB72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC72" t="s">
         <v>100</v>
@@ -6571,7 +6571,7 @@
         <v>5</v>
       </c>
       <c r="BB73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC73" t="s">
         <v>100</v>
@@ -6645,7 +6645,7 @@
         <v>5</v>
       </c>
       <c r="BB74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC74" t="s">
         <v>100</v>
@@ -6719,7 +6719,7 @@
         <v>5</v>
       </c>
       <c r="BB75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC75" t="s">
         <v>100</v>
@@ -6793,7 +6793,7 @@
         <v>5</v>
       </c>
       <c r="BB76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC76" t="s">
         <v>100</v>
@@ -6867,7 +6867,7 @@
         <v>3</v>
       </c>
       <c r="BB77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC77" t="s">
         <v>193</v>
@@ -6941,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="BB78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC78" t="s">
         <v>204</v>
@@ -7012,7 +7012,7 @@
         <v>3</v>
       </c>
       <c r="BB79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC79" t="s">
         <v>210</v>
@@ -7086,7 +7086,7 @@
         <v>4</v>
       </c>
       <c r="BB80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="s">
         <v>219</v>
@@ -7163,7 +7163,7 @@
         <v>2</v>
       </c>
       <c r="BB81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC81" t="s">
         <v>227</v>
@@ -7240,7 +7240,7 @@
         <v>2</v>
       </c>
       <c r="BB82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="s">
         <v>236</v>

--- a/data/sources/countries/honduras.xlsx
+++ b/data/sources/countries/honduras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESE_39\Downloads\Entrega ICLAC_IMFD-20260518T163702Z-3-001\países_finales_copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6063A30A-C9EB-4538-8603-BCFDF530500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D6BF24-4963-49E8-8F27-246324162B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="221">
   <si>
     <t>Id_Investment</t>
   </si>
@@ -315,9 +315,6 @@
     <t>HND-0004</t>
   </si>
   <si>
-    <t>15.41178275387732, -88.55224307150368</t>
-  </si>
-  <si>
     <t>Consorcio Sinohydro Corporation Limited (China) + Equipos Industriales S.A. (Honduras)</t>
   </si>
   <si>
@@ -333,258 +330,42 @@
     <t>https://proceso.hn/enee-adjudica-proyecto-de-transmision-mas-importante-del-litoral-hondureno/</t>
   </si>
   <si>
-    <t>15.35670354947725, -88.62476277732054</t>
-  </si>
-  <si>
-    <t>15.32682853940727, -88.6761433139229</t>
-  </si>
-  <si>
-    <t>15.28431195488705, -88.72463416892958</t>
-  </si>
-  <si>
-    <t>15.26559460181512, -88.76065624478443</t>
-  </si>
-  <si>
-    <t>15.22011578831051, -88.77259452766516</t>
-  </si>
-  <si>
-    <t>15.16307201490769, -88.83110607916896</t>
-  </si>
-  <si>
-    <t>15.12057704578278, -88.85262699605686</t>
-  </si>
-  <si>
-    <t>15.06275975942378, -88.86161774924184</t>
-  </si>
-  <si>
-    <t>15.00564913181176, -88.83946721359955</t>
-  </si>
-  <si>
-    <t>14.95565358444325, -88.82794141258759</t>
-  </si>
-  <si>
     <t>HN-CO</t>
   </si>
   <si>
     <t>COPÁN</t>
   </si>
   <si>
-    <t>14.9182994804332, -88.84610300079771</t>
-  </si>
-  <si>
-    <t>14.85609472399249, -88.85851662985783</t>
-  </si>
-  <si>
-    <t>15.786607, -86.395087</t>
-  </si>
-  <si>
-    <t>15.80937989999996, -86.48009</t>
-  </si>
-  <si>
-    <t>15.81493709999996, -86.5096656</t>
-  </si>
-  <si>
     <t>HN-AT</t>
   </si>
   <si>
     <t>ATLÁNTIDA</t>
   </si>
   <si>
-    <t>15.78663915007976, -86.55207087873467</t>
-  </si>
-  <si>
-    <t>15.76807312409048, -86.58779318073915</t>
-  </si>
-  <si>
-    <t>15.7566579061139, -86.6593882965394</t>
-  </si>
-  <si>
-    <t>15.73556616841899, -86.73792252086655</t>
-  </si>
-  <si>
-    <t>15.70333280335753, -86.80575962918584</t>
-  </si>
-  <si>
-    <t>15.64123191923856, -86.84646169022257</t>
-  </si>
-  <si>
-    <t>15.58542429634853, -86.87522780504632</t>
-  </si>
-  <si>
-    <t>15.55735401753599, -86.91763761148307</t>
-  </si>
-  <si>
-    <t>15.52717801763281, -86.94666050612618</t>
-  </si>
-  <si>
-    <t>15.48900531844916, -87.02600341496749</t>
-  </si>
-  <si>
-    <t>15.479754494647, -87.11072200295182</t>
-  </si>
-  <si>
-    <t>15.40908752185491, -87.12766456353785</t>
-  </si>
-  <si>
-    <t>15.40317205163642, -87.19134845644041</t>
-  </si>
-  <si>
-    <t>15.78280029999997, -86.8023595</t>
-  </si>
-  <si>
-    <t>15.75066944468452, -86.79052507493121</t>
-  </si>
-  <si>
-    <t>15.724673610499, -86.77711971979959</t>
-  </si>
-  <si>
-    <t>14.32942178086754, -88.4694818136123</t>
-  </si>
-  <si>
     <t>INTIBUCÁ</t>
   </si>
   <si>
-    <t>14.34280781485911, -88.31818071189181</t>
-  </si>
-  <si>
     <t>HN-IN</t>
   </si>
   <si>
-    <t>14.38082268709208, -88.2069910312816</t>
-  </si>
-  <si>
     <t>COMAYAGUA</t>
   </si>
   <si>
-    <t>14.40195655275153, -88.1385360199046</t>
-  </si>
-  <si>
     <t>HN-CM</t>
   </si>
   <si>
-    <t>14.37311637281547, -88.09008944879619</t>
-  </si>
-  <si>
-    <t>14.36115354874944, -87.99055271860598</t>
-  </si>
-  <si>
-    <t>14.38634791761132, -87.92671311854461</t>
-  </si>
-  <si>
-    <t>14.42838667883665, -87.80313506083604</t>
-  </si>
-  <si>
-    <t>14.46614165151739, -87.70527197364413</t>
-  </si>
-  <si>
-    <t>13.55489154488413, -86.86225522018272</t>
-  </si>
-  <si>
     <t>HN-CH</t>
   </si>
   <si>
     <t>CHOLUTECA</t>
   </si>
   <si>
-    <t>13.63590633529068, -86.90081801937059</t>
-  </si>
-  <si>
-    <t>13.71315087182344, -86.8889285310737</t>
-  </si>
-  <si>
     <t>HN-EP</t>
   </si>
   <si>
     <t>EL PARAÍSO</t>
   </si>
   <si>
-    <t>13.81092628255706, -86.86456965312864</t>
-  </si>
-  <si>
-    <t>13.88834874490429, -86.8948483236708</t>
-  </si>
-  <si>
-    <t>13.94541065610418, -86.9461378594499</t>
-  </si>
-  <si>
-    <t>13.94105994070511, -87.03488045697975</t>
-  </si>
-  <si>
-    <t>13.99425078801625, -87.0355407085932</t>
-  </si>
-  <si>
-    <t>14.09678220487307, -87.01987553251685</t>
-  </si>
-  <si>
-    <t>14.19126700486824, -87.03380790469441</t>
-  </si>
-  <si>
-    <t>14.24036102051354, -87.15351585314349</t>
-  </si>
-  <si>
-    <t>14.17891426379843, -87.03789410389894</t>
-  </si>
-  <si>
-    <t>14.20371706032203, -86.99149748668702</t>
-  </si>
-  <si>
-    <t>14.26572292528283, -86.88602192283616</t>
-  </si>
-  <si>
-    <t>14.27011489176048, -86.72469035315493</t>
-  </si>
-  <si>
-    <t>14.23727076888533, -86.64383547932859</t>
-  </si>
-  <si>
-    <t>14.23322108567361, -86.58443963156621</t>
-  </si>
-  <si>
-    <t>14.27454494781644, -86.38102758457211</t>
-  </si>
-  <si>
-    <t>14.30341046343454, -86.33864433427033</t>
-  </si>
-  <si>
-    <t>14.35706254342533, -86.27923927391929</t>
-  </si>
-  <si>
-    <t>14.46458370664412, -86.17711203358625</t>
-  </si>
-  <si>
-    <t>14.60568017715797, -86.07872090145861</t>
-  </si>
-  <si>
-    <t>14.66395732123546, -86.05714972907238</t>
-  </si>
-  <si>
-    <t>15.13314257495967, -88.30513362208707</t>
-  </si>
-  <si>
-    <t>15.10759373066058, -88.31725941451553</t>
-  </si>
-  <si>
-    <t>15.06505370140019, -88.33745879464591</t>
-  </si>
-  <si>
-    <t>14.90831695178042, -88.3179309823655</t>
-  </si>
-  <si>
-    <t>HN-SB</t>
-  </si>
-  <si>
-    <t>SANTA BÁRBARA</t>
-  </si>
-  <si>
-    <t>14.91280930906046, -88.20008350336222</t>
-  </si>
-  <si>
-    <t>14.81187049484361, -88.10487423245286</t>
-  </si>
-  <si>
-    <t>14.83307483338753, -88.04036595146063</t>
-  </si>
-  <si>
     <t>HND-0005</t>
   </si>
   <si>
@@ -736,6 +517,177 @@
   </si>
   <si>
     <t>https://www.expedientepublico.org/honduras-esconde-informacion-de-proyecto-de-us80-millones-con-china/</t>
+  </si>
+  <si>
+    <t>13.25612400834732, -87.14265333360723</t>
+  </si>
+  <si>
+    <t>13.37224542788409, -86.99109859256755</t>
+  </si>
+  <si>
+    <t>13.42841722024538, -86.91551247662898</t>
+  </si>
+  <si>
+    <t>13.48050936161675, -86.91806178235902</t>
+  </si>
+  <si>
+    <t>13.53656599301242, -86.92733584455013</t>
+  </si>
+  <si>
+    <t>13.62114157433687, -86.90584919553905</t>
+  </si>
+  <si>
+    <t>13.67851821590115, -86.89025804410657</t>
+  </si>
+  <si>
+    <t>13.77151259824581, -86.93167182286219</t>
+  </si>
+  <si>
+    <t>13.79487286404392, -87.00743247363894</t>
+  </si>
+  <si>
+    <t>13.89230212664705, -87.02019075140991</t>
+  </si>
+  <si>
+    <t>14.01582599197026, -87.01654155342851</t>
+  </si>
+  <si>
+    <t>14.04624177166116, -86.8830227901887</t>
+  </si>
+  <si>
+    <t>14.06738697637386, -86.7220157583542</t>
+  </si>
+  <si>
+    <t>14.02735278538261, -86.61232746600714</t>
+  </si>
+  <si>
+    <t>14.0274415967707, -86.4495612192376</t>
+  </si>
+  <si>
+    <t>14.04902902634157, -86.29895820182097</t>
+  </si>
+  <si>
+    <t>14.21394784348763, -86.17800786337835</t>
+  </si>
+  <si>
+    <t>14.37750444018253, -86.04269397703625</t>
+  </si>
+  <si>
+    <t>14.26005561995681, -88.41870125690289</t>
+  </si>
+  <si>
+    <t>14.25875299666088, -88.25744468765701</t>
+  </si>
+  <si>
+    <t>14.2912325419656, -88.13665692489147</t>
+  </si>
+  <si>
+    <t>14.25545425805024, -87.97899696271558</t>
+  </si>
+  <si>
+    <t>14.28639327401731, -87.70577679125374</t>
+  </si>
+  <si>
+    <t>14.31402233624371, -87.61813553121662</t>
+  </si>
+  <si>
+    <t>15.67312754427035, -86.70508168583122</t>
+  </si>
+  <si>
+    <t>15.59833007147057, -86.67601327651967</t>
+  </si>
+  <si>
+    <t>15.49253384951398, -86.64616952227068</t>
+  </si>
+  <si>
+    <t>15.4378577186896, -86.65101550603015</t>
+  </si>
+  <si>
+    <t>15.35966605029214, -86.70421229633108</t>
+  </si>
+  <si>
+    <t>15.2732501092217, -86.7402848390501</t>
+  </si>
+  <si>
+    <t>15.19583194266781, -86.88573618757631</t>
+  </si>
+  <si>
+    <t>15.21325806526725, -86.97312041069114</t>
+  </si>
+  <si>
+    <t>15.08577083192691, -87.1369490746547</t>
+  </si>
+  <si>
+    <t>15.1872630810112, -87.37388967126458</t>
+  </si>
+  <si>
+    <t>15.28483530358733, -87.47626978392658</t>
+  </si>
+  <si>
+    <t>15.27823104658389, -87.65172807978401</t>
+  </si>
+  <si>
+    <t>15.31861414798511, -87.77000970837003</t>
+  </si>
+  <si>
+    <t>15.44489272169599, -87.88529110020339</t>
+  </si>
+  <si>
+    <t>15.53997668394544, -87.91008385253568</t>
+  </si>
+  <si>
+    <t>15.73725963430914, -87.82996239192815</t>
+  </si>
+  <si>
+    <t>15.51912293807608, -87.90813373624114</t>
+  </si>
+  <si>
+    <t>15.45456786316112, -87.96347199552196</t>
+  </si>
+  <si>
+    <t>15.31561667040701, -87.94933711586057</t>
+  </si>
+  <si>
+    <t>15.22100271062271, -87.92820977435956</t>
+  </si>
+  <si>
+    <t>15.12360297998642, -87.91454861700429</t>
+  </si>
+  <si>
+    <t>15.04611850402629, -87.93511730759705</t>
+  </si>
+  <si>
+    <t>14.98986284548969, -88.00766716674742</t>
+  </si>
+  <si>
+    <t>14.8511467862384, -88.0368020466916</t>
+  </si>
+  <si>
+    <t>14.7635103398171, -88.1047859553892</t>
+  </si>
+  <si>
+    <t>15.00045062026079, -88.18965935753637</t>
+  </si>
+  <si>
+    <t>14.95571410414166, -88.18964214056224</t>
+  </si>
+  <si>
+    <t>14.94394227102848, -88.21571155833726</t>
+  </si>
+  <si>
+    <t>14.79580791320798, -88.21326190433354</t>
+  </si>
+  <si>
+    <t>14.76611598958155, -88.09383295098095</t>
+  </si>
+  <si>
+    <t>14.73347149911211, -88.07144359917208</t>
+  </si>
+  <si>
+    <t>14.65660248432223, -88.0098092809416</t>
+  </si>
+  <si>
+    <t>14.67715247153414, -87.91882097591301</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE82"/>
+  <dimension ref="A1:BE68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.3">
@@ -1556,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
@@ -1574,7 +1526,7 @@
         <v>2024</v>
       </c>
       <c r="J6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -1589,10 +1541,10 @@
         <v>66</v>
       </c>
       <c r="O6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" t="s">
         <v>98</v>
-      </c>
-      <c r="P6" t="s">
-        <v>99</v>
       </c>
       <c r="Q6" t="s">
         <v>90</v>
@@ -1616,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE6" t="s">
         <v>100</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.3">
@@ -1630,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>59</v>
@@ -1648,7 +1600,7 @@
         <v>2024</v>
       </c>
       <c r="J7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -1663,10 +1615,10 @@
         <v>66</v>
       </c>
       <c r="O7" t="s">
+        <v>97</v>
+      </c>
+      <c r="P7" t="s">
         <v>98</v>
-      </c>
-      <c r="P7" t="s">
-        <v>99</v>
       </c>
       <c r="Q7" t="s">
         <v>90</v>
@@ -1690,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE7" t="s">
         <v>100</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.3">
@@ -1704,7 +1656,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
         <v>59</v>
@@ -1722,7 +1674,7 @@
         <v>2024</v>
       </c>
       <c r="J8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -1737,10 +1689,10 @@
         <v>66</v>
       </c>
       <c r="O8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P8" t="s">
         <v>98</v>
-      </c>
-      <c r="P8" t="s">
-        <v>99</v>
       </c>
       <c r="Q8" t="s">
         <v>90</v>
@@ -1764,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="BC8" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE8" t="s">
         <v>100</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.3">
@@ -1778,7 +1730,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="E9" t="s">
         <v>59</v>
@@ -1796,7 +1748,7 @@
         <v>2024</v>
       </c>
       <c r="J9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
@@ -1811,10 +1763,10 @@
         <v>66</v>
       </c>
       <c r="O9" t="s">
+        <v>97</v>
+      </c>
+      <c r="P9" t="s">
         <v>98</v>
-      </c>
-      <c r="P9" t="s">
-        <v>99</v>
       </c>
       <c r="Q9" t="s">
         <v>90</v>
@@ -1838,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE9" t="s">
         <v>100</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.3">
@@ -1852,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="E10" t="s">
         <v>59</v>
@@ -1870,7 +1822,7 @@
         <v>2024</v>
       </c>
       <c r="J10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10" t="s">
         <v>10</v>
@@ -1885,10 +1837,10 @@
         <v>66</v>
       </c>
       <c r="O10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" t="s">
         <v>98</v>
-      </c>
-      <c r="P10" t="s">
-        <v>99</v>
       </c>
       <c r="Q10" t="s">
         <v>90</v>
@@ -1912,10 +1864,10 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE10" t="s">
         <v>100</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.3">
@@ -1926,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="E11" t="s">
         <v>59</v>
@@ -1944,7 +1896,7 @@
         <v>2024</v>
       </c>
       <c r="J11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
@@ -1959,10 +1911,10 @@
         <v>66</v>
       </c>
       <c r="O11" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" t="s">
         <v>98</v>
-      </c>
-      <c r="P11" t="s">
-        <v>99</v>
       </c>
       <c r="Q11" t="s">
         <v>90</v>
@@ -1986,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="BC11" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE11" t="s">
         <v>100</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.3">
@@ -2000,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
         <v>59</v>
@@ -2018,7 +1970,7 @@
         <v>2024</v>
       </c>
       <c r="J12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s">
         <v>10</v>
@@ -2033,10 +1985,10 @@
         <v>66</v>
       </c>
       <c r="O12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" t="s">
         <v>98</v>
-      </c>
-      <c r="P12" t="s">
-        <v>99</v>
       </c>
       <c r="Q12" t="s">
         <v>90</v>
@@ -2060,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE12" t="s">
         <v>100</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.3">
@@ -2074,7 +2026,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
         <v>59</v>
@@ -2092,7 +2044,7 @@
         <v>2024</v>
       </c>
       <c r="J13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
@@ -2107,10 +2059,10 @@
         <v>66</v>
       </c>
       <c r="O13" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" t="s">
         <v>98</v>
-      </c>
-      <c r="P13" t="s">
-        <v>99</v>
       </c>
       <c r="Q13" t="s">
         <v>90</v>
@@ -2134,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE13" t="s">
         <v>100</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.3">
@@ -2148,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
@@ -2166,7 +2118,7 @@
         <v>2024</v>
       </c>
       <c r="J14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
         <v>10</v>
@@ -2181,10 +2133,10 @@
         <v>66</v>
       </c>
       <c r="O14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P14" t="s">
         <v>98</v>
-      </c>
-      <c r="P14" t="s">
-        <v>99</v>
       </c>
       <c r="Q14" t="s">
         <v>90</v>
@@ -2208,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE14" t="s">
         <v>100</v>
-      </c>
-      <c r="BE14" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.3">
@@ -2222,7 +2174,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
@@ -2240,7 +2192,7 @@
         <v>2024</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K15" t="s">
         <v>10</v>
@@ -2255,10 +2207,10 @@
         <v>66</v>
       </c>
       <c r="O15" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" t="s">
         <v>98</v>
-      </c>
-      <c r="P15" t="s">
-        <v>99</v>
       </c>
       <c r="Q15" t="s">
         <v>90</v>
@@ -2282,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE15" t="s">
         <v>100</v>
-      </c>
-      <c r="BE15" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.3">
@@ -2296,7 +2248,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>59</v>
@@ -2308,13 +2260,13 @@
         <v>61</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I16">
         <v>2024</v>
       </c>
       <c r="J16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K16" t="s">
         <v>10</v>
@@ -2329,13 +2281,13 @@
         <v>66</v>
       </c>
       <c r="O16" t="s">
+        <v>97</v>
+      </c>
+      <c r="P16" t="s">
         <v>98</v>
       </c>
-      <c r="P16" t="s">
-        <v>99</v>
-      </c>
       <c r="Q16" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="R16">
         <v>115</v>
@@ -2356,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE16" t="s">
         <v>100</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:57" x14ac:dyDescent="0.3">
@@ -2370,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
         <v>59</v>
@@ -2382,13 +2334,13 @@
         <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I17">
         <v>2024</v>
       </c>
       <c r="J17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s">
         <v>10</v>
@@ -2403,13 +2355,13 @@
         <v>66</v>
       </c>
       <c r="O17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" t="s">
         <v>98</v>
       </c>
-      <c r="P17" t="s">
-        <v>99</v>
-      </c>
       <c r="Q17" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="R17">
         <v>115</v>
@@ -2430,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE17" t="s">
         <v>100</v>
-      </c>
-      <c r="BE17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:57" x14ac:dyDescent="0.3">
@@ -2444,7 +2396,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="E18" t="s">
         <v>59</v>
@@ -2456,13 +2408,13 @@
         <v>61</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I18">
         <v>2024</v>
       </c>
       <c r="J18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s">
         <v>10</v>
@@ -2477,13 +2429,13 @@
         <v>66</v>
       </c>
       <c r="O18" t="s">
+        <v>97</v>
+      </c>
+      <c r="P18" t="s">
         <v>98</v>
       </c>
-      <c r="P18" t="s">
-        <v>99</v>
-      </c>
       <c r="Q18" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="R18">
         <v>115</v>
@@ -2504,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE18" t="s">
         <v>100</v>
-      </c>
-      <c r="BE18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:57" x14ac:dyDescent="0.3">
@@ -2518,7 +2470,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="E19" t="s">
         <v>59</v>
@@ -2536,7 +2488,7 @@
         <v>2024</v>
       </c>
       <c r="J19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s">
         <v>10</v>
@@ -2551,10 +2503,10 @@
         <v>66</v>
       </c>
       <c r="O19" t="s">
+        <v>97</v>
+      </c>
+      <c r="P19" t="s">
         <v>98</v>
-      </c>
-      <c r="P19" t="s">
-        <v>99</v>
       </c>
       <c r="Q19" t="s">
         <v>69</v>
@@ -2578,10 +2530,10 @@
         <v>0</v>
       </c>
       <c r="BC19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE19" t="s">
         <v>100</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:57" x14ac:dyDescent="0.3">
@@ -2592,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
         <v>59</v>
@@ -2610,7 +2562,7 @@
         <v>2024</v>
       </c>
       <c r="J20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s">
         <v>10</v>
@@ -2625,10 +2577,10 @@
         <v>66</v>
       </c>
       <c r="O20" t="s">
+        <v>97</v>
+      </c>
+      <c r="P20" t="s">
         <v>98</v>
-      </c>
-      <c r="P20" t="s">
-        <v>99</v>
       </c>
       <c r="Q20" t="s">
         <v>69</v>
@@ -2652,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="BC20" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE20" t="s">
         <v>100</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:57" x14ac:dyDescent="0.3">
@@ -2666,7 +2618,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="E21" t="s">
         <v>59</v>
@@ -2678,13 +2630,13 @@
         <v>61</v>
       </c>
       <c r="H21" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I21">
         <v>2024</v>
       </c>
       <c r="J21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s">
         <v>10</v>
@@ -2699,13 +2651,13 @@
         <v>66</v>
       </c>
       <c r="O21" t="s">
+        <v>97</v>
+      </c>
+      <c r="P21" t="s">
         <v>98</v>
       </c>
-      <c r="P21" t="s">
-        <v>99</v>
-      </c>
       <c r="Q21" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R21">
         <v>115</v>
@@ -2726,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="BC21" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE21" t="s">
         <v>100</v>
-      </c>
-      <c r="BE21" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:57" x14ac:dyDescent="0.3">
@@ -2740,7 +2692,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="E22" t="s">
         <v>59</v>
@@ -2752,13 +2704,13 @@
         <v>61</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I22">
         <v>2024</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K22" t="s">
         <v>10</v>
@@ -2773,13 +2725,13 @@
         <v>66</v>
       </c>
       <c r="O22" t="s">
+        <v>97</v>
+      </c>
+      <c r="P22" t="s">
         <v>98</v>
       </c>
-      <c r="P22" t="s">
-        <v>99</v>
-      </c>
       <c r="Q22" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R22">
         <v>115</v>
@@ -2800,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="BC22" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE22" t="s">
         <v>100</v>
-      </c>
-      <c r="BE22" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:57" x14ac:dyDescent="0.3">
@@ -2814,7 +2766,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
         <v>59</v>
@@ -2826,13 +2778,13 @@
         <v>61</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I23">
         <v>2024</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s">
         <v>10</v>
@@ -2847,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="O23" t="s">
+        <v>97</v>
+      </c>
+      <c r="P23" t="s">
         <v>98</v>
       </c>
-      <c r="P23" t="s">
-        <v>99</v>
-      </c>
       <c r="Q23" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R23">
         <v>115</v>
@@ -2874,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="BC23" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE23" t="s">
         <v>100</v>
-      </c>
-      <c r="BE23" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:57" x14ac:dyDescent="0.3">
@@ -2888,7 +2840,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
         <v>59</v>
@@ -2900,19 +2852,19 @@
         <v>61</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I24">
         <v>2024</v>
       </c>
       <c r="J24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" t="s">
         <v>65</v>
@@ -2921,13 +2873,13 @@
         <v>66</v>
       </c>
       <c r="O24" t="s">
+        <v>97</v>
+      </c>
+      <c r="P24" t="s">
         <v>98</v>
       </c>
-      <c r="P24" t="s">
-        <v>99</v>
-      </c>
       <c r="Q24" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R24">
         <v>115</v>
@@ -2948,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="BC24" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE24" t="s">
         <v>100</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:57" x14ac:dyDescent="0.3">
@@ -2962,7 +2914,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
         <v>59</v>
@@ -2974,19 +2926,19 @@
         <v>61</v>
       </c>
       <c r="H25" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I25">
         <v>2024</v>
       </c>
       <c r="J25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s">
         <v>10</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" t="s">
         <v>65</v>
@@ -2995,13 +2947,13 @@
         <v>66</v>
       </c>
       <c r="O25" t="s">
+        <v>97</v>
+      </c>
+      <c r="P25" t="s">
         <v>98</v>
       </c>
-      <c r="P25" t="s">
-        <v>99</v>
-      </c>
       <c r="Q25" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R25">
         <v>115</v>
@@ -3022,10 +2974,10 @@
         <v>0</v>
       </c>
       <c r="BC25" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE25" t="s">
         <v>100</v>
-      </c>
-      <c r="BE25" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:57" x14ac:dyDescent="0.3">
@@ -3036,7 +2988,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="E26" t="s">
         <v>59</v>
@@ -3048,19 +3000,19 @@
         <v>61</v>
       </c>
       <c r="H26" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I26">
         <v>2024</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K26" t="s">
         <v>10</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="s">
         <v>65</v>
@@ -3069,13 +3021,13 @@
         <v>66</v>
       </c>
       <c r="O26" t="s">
+        <v>97</v>
+      </c>
+      <c r="P26" t="s">
         <v>98</v>
       </c>
-      <c r="P26" t="s">
-        <v>99</v>
-      </c>
       <c r="Q26" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R26">
         <v>115</v>
@@ -3096,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="BC26" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE26" t="s">
         <v>100</v>
-      </c>
-      <c r="BE26" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:57" x14ac:dyDescent="0.3">
@@ -3110,7 +3062,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>59</v>
@@ -3122,19 +3074,19 @@
         <v>61</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I27">
         <v>2024</v>
       </c>
       <c r="J27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K27" t="s">
         <v>10</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="s">
         <v>65</v>
@@ -3143,13 +3095,13 @@
         <v>66</v>
       </c>
       <c r="O27" t="s">
+        <v>97</v>
+      </c>
+      <c r="P27" t="s">
         <v>98</v>
       </c>
-      <c r="P27" t="s">
-        <v>99</v>
-      </c>
       <c r="Q27" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R27">
         <v>115</v>
@@ -3170,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="BC27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE27" t="s">
         <v>100</v>
-      </c>
-      <c r="BE27" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:57" x14ac:dyDescent="0.3">
@@ -3184,7 +3136,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>59</v>
@@ -3196,19 +3148,19 @@
         <v>61</v>
       </c>
       <c r="H28" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I28">
         <v>2024</v>
       </c>
       <c r="J28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K28" t="s">
         <v>10</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="s">
         <v>65</v>
@@ -3217,13 +3169,13 @@
         <v>66</v>
       </c>
       <c r="O28" t="s">
+        <v>97</v>
+      </c>
+      <c r="P28" t="s">
         <v>98</v>
       </c>
-      <c r="P28" t="s">
-        <v>99</v>
-      </c>
       <c r="Q28" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R28">
         <v>115</v>
@@ -3244,10 +3196,10 @@
         <v>0</v>
       </c>
       <c r="BC28" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE28" t="s">
         <v>100</v>
-      </c>
-      <c r="BE28" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:57" x14ac:dyDescent="0.3">
@@ -3258,7 +3210,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="E29" t="s">
         <v>59</v>
@@ -3270,19 +3222,19 @@
         <v>61</v>
       </c>
       <c r="H29" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I29">
         <v>2024</v>
       </c>
       <c r="J29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K29" t="s">
         <v>10</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" t="s">
         <v>65</v>
@@ -3291,13 +3243,13 @@
         <v>66</v>
       </c>
       <c r="O29" t="s">
+        <v>97</v>
+      </c>
+      <c r="P29" t="s">
         <v>98</v>
       </c>
-      <c r="P29" t="s">
-        <v>99</v>
-      </c>
       <c r="Q29" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R29">
         <v>115</v>
@@ -3318,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="BC29" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE29" t="s">
         <v>100</v>
-      </c>
-      <c r="BE29" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:57" x14ac:dyDescent="0.3">
@@ -3332,7 +3284,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
         <v>59</v>
@@ -3344,19 +3296,19 @@
         <v>61</v>
       </c>
       <c r="H30" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I30">
         <v>2024</v>
       </c>
       <c r="J30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s">
         <v>10</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30" t="s">
         <v>65</v>
@@ -3365,13 +3317,13 @@
         <v>66</v>
       </c>
       <c r="O30" t="s">
+        <v>97</v>
+      </c>
+      <c r="P30" t="s">
         <v>98</v>
       </c>
-      <c r="P30" t="s">
-        <v>99</v>
-      </c>
       <c r="Q30" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R30">
         <v>115</v>
@@ -3392,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="BC30" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE30" t="s">
         <v>100</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:57" x14ac:dyDescent="0.3">
@@ -3406,7 +3358,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="E31" t="s">
         <v>59</v>
@@ -3418,19 +3370,19 @@
         <v>61</v>
       </c>
       <c r="H31" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I31">
         <v>2024</v>
       </c>
       <c r="J31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K31" t="s">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31" t="s">
         <v>65</v>
@@ -3439,13 +3391,13 @@
         <v>66</v>
       </c>
       <c r="O31" t="s">
+        <v>97</v>
+      </c>
+      <c r="P31" t="s">
         <v>98</v>
       </c>
-      <c r="P31" t="s">
-        <v>99</v>
-      </c>
       <c r="Q31" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R31">
         <v>115</v>
@@ -3466,10 +3418,10 @@
         <v>0</v>
       </c>
       <c r="BC31" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE31" t="s">
         <v>100</v>
-      </c>
-      <c r="BE31" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:57" x14ac:dyDescent="0.3">
@@ -3480,7 +3432,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="E32" t="s">
         <v>59</v>
@@ -3492,19 +3444,19 @@
         <v>61</v>
       </c>
       <c r="H32" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I32">
         <v>2024</v>
       </c>
       <c r="J32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K32" t="s">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32" t="s">
         <v>65</v>
@@ -3513,13 +3465,13 @@
         <v>66</v>
       </c>
       <c r="O32" t="s">
+        <v>97</v>
+      </c>
+      <c r="P32" t="s">
         <v>98</v>
       </c>
-      <c r="P32" t="s">
-        <v>99</v>
-      </c>
       <c r="Q32" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R32">
         <v>115</v>
@@ -3540,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="BC32" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE32" t="s">
         <v>100</v>
-      </c>
-      <c r="BE32" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:57" x14ac:dyDescent="0.3">
@@ -3554,7 +3506,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="E33" t="s">
         <v>59</v>
@@ -3566,19 +3518,19 @@
         <v>61</v>
       </c>
       <c r="H33" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I33">
         <v>2024</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K33" t="s">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M33" t="s">
         <v>65</v>
@@ -3587,13 +3539,13 @@
         <v>66</v>
       </c>
       <c r="O33" t="s">
+        <v>97</v>
+      </c>
+      <c r="P33" t="s">
         <v>98</v>
       </c>
-      <c r="P33" t="s">
-        <v>99</v>
-      </c>
       <c r="Q33" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R33">
         <v>115</v>
@@ -3614,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="BC33" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE33" t="s">
         <v>100</v>
-      </c>
-      <c r="BE33" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:57" x14ac:dyDescent="0.3">
@@ -3628,7 +3580,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="E34" t="s">
         <v>59</v>
@@ -3640,19 +3592,19 @@
         <v>61</v>
       </c>
       <c r="H34" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I34">
         <v>2024</v>
       </c>
       <c r="J34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K34" t="s">
         <v>10</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" t="s">
         <v>65</v>
@@ -3661,13 +3613,13 @@
         <v>66</v>
       </c>
       <c r="O34" t="s">
+        <v>97</v>
+      </c>
+      <c r="P34" t="s">
         <v>98</v>
       </c>
-      <c r="P34" t="s">
-        <v>99</v>
-      </c>
       <c r="Q34" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R34">
         <v>115</v>
@@ -3688,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="BC34" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE34" t="s">
         <v>100</v>
-      </c>
-      <c r="BE34" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:57" x14ac:dyDescent="0.3">
@@ -3702,7 +3654,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="E35" t="s">
         <v>59</v>
@@ -3714,19 +3666,19 @@
         <v>61</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I35">
         <v>2024</v>
       </c>
       <c r="J35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s">
         <v>10</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" t="s">
         <v>65</v>
@@ -3735,13 +3687,13 @@
         <v>66</v>
       </c>
       <c r="O35" t="s">
+        <v>97</v>
+      </c>
+      <c r="P35" t="s">
         <v>98</v>
       </c>
-      <c r="P35" t="s">
-        <v>99</v>
-      </c>
       <c r="Q35" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R35">
         <v>115</v>
@@ -3762,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="BC35" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE35" t="s">
         <v>100</v>
-      </c>
-      <c r="BE35" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:57" x14ac:dyDescent="0.3">
@@ -3776,7 +3728,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
         <v>59</v>
@@ -3788,19 +3740,19 @@
         <v>61</v>
       </c>
       <c r="H36" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I36">
         <v>2024</v>
       </c>
       <c r="J36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K36" t="s">
         <v>10</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" t="s">
         <v>65</v>
@@ -3809,13 +3761,13 @@
         <v>66</v>
       </c>
       <c r="O36" t="s">
+        <v>97</v>
+      </c>
+      <c r="P36" t="s">
         <v>98</v>
       </c>
-      <c r="P36" t="s">
-        <v>99</v>
-      </c>
       <c r="Q36" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R36">
         <v>115</v>
@@ -3836,10 +3788,10 @@
         <v>0</v>
       </c>
       <c r="BC36" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE36" t="s">
         <v>100</v>
-      </c>
-      <c r="BE36" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:57" x14ac:dyDescent="0.3">
@@ -3850,7 +3802,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="E37" t="s">
         <v>59</v>
@@ -3862,19 +3814,19 @@
         <v>61</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I37">
         <v>2024</v>
       </c>
       <c r="J37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K37" t="s">
         <v>10</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37" t="s">
         <v>65</v>
@@ -3883,13 +3835,13 @@
         <v>66</v>
       </c>
       <c r="O37" t="s">
+        <v>97</v>
+      </c>
+      <c r="P37" t="s">
         <v>98</v>
       </c>
-      <c r="P37" t="s">
-        <v>99</v>
-      </c>
       <c r="Q37" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R37">
         <v>115</v>
@@ -3910,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="BC37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE37" t="s">
         <v>100</v>
-      </c>
-      <c r="BE37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:57" x14ac:dyDescent="0.3">
@@ -3924,7 +3876,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="E38" t="s">
         <v>59</v>
@@ -3936,19 +3888,19 @@
         <v>61</v>
       </c>
       <c r="H38" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I38">
         <v>2024</v>
       </c>
       <c r="J38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K38" t="s">
         <v>10</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" t="s">
         <v>65</v>
@@ -3957,13 +3909,13 @@
         <v>66</v>
       </c>
       <c r="O38" t="s">
+        <v>97</v>
+      </c>
+      <c r="P38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" t="s">
-        <v>99</v>
-      </c>
       <c r="Q38" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="R38">
         <v>115</v>
@@ -3984,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="BC38" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE38" t="s">
         <v>100</v>
-      </c>
-      <c r="BE38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:57" x14ac:dyDescent="0.3">
@@ -3998,7 +3950,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="E39" t="s">
         <v>59</v>
@@ -4010,19 +3962,19 @@
         <v>61</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I39">
         <v>2024</v>
       </c>
       <c r="J39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K39" t="s">
         <v>10</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M39" t="s">
         <v>65</v>
@@ -4031,13 +3983,13 @@
         <v>66</v>
       </c>
       <c r="O39" t="s">
+        <v>97</v>
+      </c>
+      <c r="P39" t="s">
         <v>98</v>
       </c>
-      <c r="P39" t="s">
-        <v>99</v>
-      </c>
       <c r="Q39" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="R39">
         <v>115</v>
@@ -4058,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="BC39" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE39" t="s">
         <v>100</v>
-      </c>
-      <c r="BE39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:57" x14ac:dyDescent="0.3">
@@ -4072,7 +4024,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="E40" t="s">
         <v>59</v>
@@ -4084,19 +4036,19 @@
         <v>61</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I40">
         <v>2024</v>
       </c>
       <c r="J40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K40" t="s">
         <v>10</v>
       </c>
       <c r="L40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" t="s">
         <v>65</v>
@@ -4105,13 +4057,13 @@
         <v>66</v>
       </c>
       <c r="O40" t="s">
+        <v>97</v>
+      </c>
+      <c r="P40" t="s">
         <v>98</v>
       </c>
-      <c r="P40" t="s">
-        <v>99</v>
-      </c>
       <c r="Q40" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R40">
         <v>115</v>
@@ -4132,10 +4084,10 @@
         <v>0</v>
       </c>
       <c r="BC40" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE40" t="s">
         <v>100</v>
-      </c>
-      <c r="BE40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:57" x14ac:dyDescent="0.3">
@@ -4146,7 +4098,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="E41" t="s">
         <v>59</v>
@@ -4158,19 +4110,19 @@
         <v>61</v>
       </c>
       <c r="H41" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I41">
         <v>2024</v>
       </c>
       <c r="J41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K41" t="s">
         <v>10</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M41" t="s">
         <v>65</v>
@@ -4179,13 +4131,13 @@
         <v>66</v>
       </c>
       <c r="O41" t="s">
+        <v>97</v>
+      </c>
+      <c r="P41" t="s">
         <v>98</v>
       </c>
-      <c r="P41" t="s">
-        <v>99</v>
-      </c>
       <c r="Q41" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R41">
         <v>115</v>
@@ -4206,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="BC41" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE41" t="s">
         <v>100</v>
-      </c>
-      <c r="BE41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:57" x14ac:dyDescent="0.3">
@@ -4220,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
         <v>59</v>
@@ -4232,19 +4184,19 @@
         <v>61</v>
       </c>
       <c r="H42" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I42">
         <v>2024</v>
       </c>
       <c r="J42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s">
         <v>10</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M42" t="s">
         <v>65</v>
@@ -4253,13 +4205,13 @@
         <v>66</v>
       </c>
       <c r="O42" t="s">
+        <v>97</v>
+      </c>
+      <c r="P42" t="s">
         <v>98</v>
       </c>
-      <c r="P42" t="s">
-        <v>99</v>
-      </c>
       <c r="Q42" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R42">
         <v>115</v>
@@ -4280,10 +4232,10 @@
         <v>0</v>
       </c>
       <c r="BC42" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE42" t="s">
         <v>100</v>
-      </c>
-      <c r="BE42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:57" x14ac:dyDescent="0.3">
@@ -4294,7 +4246,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="E43" t="s">
         <v>59</v>
@@ -4306,19 +4258,19 @@
         <v>61</v>
       </c>
       <c r="H43" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I43">
         <v>2024</v>
       </c>
       <c r="J43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s">
         <v>10</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M43" t="s">
         <v>65</v>
@@ -4327,13 +4279,13 @@
         <v>66</v>
       </c>
       <c r="O43" t="s">
+        <v>97</v>
+      </c>
+      <c r="P43" t="s">
         <v>98</v>
       </c>
-      <c r="P43" t="s">
-        <v>99</v>
-      </c>
       <c r="Q43" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R43">
         <v>115</v>
@@ -4354,10 +4306,10 @@
         <v>0</v>
       </c>
       <c r="BC43" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE43" t="s">
         <v>100</v>
-      </c>
-      <c r="BE43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:57" x14ac:dyDescent="0.3">
@@ -4368,7 +4320,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="E44" t="s">
         <v>59</v>
@@ -4380,19 +4332,19 @@
         <v>61</v>
       </c>
       <c r="H44" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I44">
         <v>2024</v>
       </c>
       <c r="J44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s">
         <v>10</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M44" t="s">
         <v>65</v>
@@ -4401,13 +4353,13 @@
         <v>66</v>
       </c>
       <c r="O44" t="s">
+        <v>97</v>
+      </c>
+      <c r="P44" t="s">
         <v>98</v>
       </c>
-      <c r="P44" t="s">
-        <v>99</v>
-      </c>
       <c r="Q44" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R44">
         <v>115</v>
@@ -4428,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="BC44" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE44" t="s">
         <v>100</v>
-      </c>
-      <c r="BE44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:57" x14ac:dyDescent="0.3">
@@ -4442,7 +4394,7 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
         <v>59</v>
@@ -4454,19 +4406,19 @@
         <v>61</v>
       </c>
       <c r="H45" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I45">
         <v>2024</v>
       </c>
       <c r="J45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s">
         <v>10</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" t="s">
         <v>65</v>
@@ -4475,13 +4427,13 @@
         <v>66</v>
       </c>
       <c r="O45" t="s">
+        <v>97</v>
+      </c>
+      <c r="P45" t="s">
         <v>98</v>
       </c>
-      <c r="P45" t="s">
-        <v>99</v>
-      </c>
       <c r="Q45" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R45">
         <v>115</v>
@@ -4502,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="BC45" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE45" t="s">
         <v>100</v>
-      </c>
-      <c r="BE45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:57" x14ac:dyDescent="0.3">
@@ -4516,7 +4468,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>204</v>
       </c>
       <c r="E46" t="s">
         <v>59</v>
@@ -4528,19 +4480,19 @@
         <v>61</v>
       </c>
       <c r="H46" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I46">
         <v>2024</v>
       </c>
       <c r="J46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s">
         <v>10</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M46" t="s">
         <v>65</v>
@@ -4549,13 +4501,13 @@
         <v>66</v>
       </c>
       <c r="O46" t="s">
+        <v>97</v>
+      </c>
+      <c r="P46" t="s">
         <v>98</v>
       </c>
-      <c r="P46" t="s">
-        <v>99</v>
-      </c>
       <c r="Q46" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="R46">
         <v>115</v>
@@ -4576,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="BC46" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE46" t="s">
         <v>100</v>
-      </c>
-      <c r="BE46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:57" x14ac:dyDescent="0.3">
@@ -4590,7 +4542,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="E47" t="s">
         <v>59</v>
@@ -4602,19 +4554,19 @@
         <v>61</v>
       </c>
       <c r="H47" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="I47">
         <v>2024</v>
       </c>
       <c r="J47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s">
         <v>10</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" t="s">
         <v>65</v>
@@ -4623,13 +4575,13 @@
         <v>66</v>
       </c>
       <c r="O47" t="s">
+        <v>97</v>
+      </c>
+      <c r="P47" t="s">
         <v>98</v>
       </c>
-      <c r="P47" t="s">
-        <v>99</v>
-      </c>
       <c r="Q47" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="R47">
         <v>115</v>
@@ -4650,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="BC47" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE47" t="s">
         <v>100</v>
-      </c>
-      <c r="BE47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:57" x14ac:dyDescent="0.3">
@@ -4664,7 +4616,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="E48" t="s">
         <v>59</v>
@@ -4676,19 +4628,19 @@
         <v>61</v>
       </c>
       <c r="H48" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="I48">
         <v>2024</v>
       </c>
       <c r="J48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s">
         <v>10</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M48" t="s">
         <v>65</v>
@@ -4697,13 +4649,13 @@
         <v>66</v>
       </c>
       <c r="O48" t="s">
+        <v>97</v>
+      </c>
+      <c r="P48" t="s">
         <v>98</v>
       </c>
-      <c r="P48" t="s">
-        <v>99</v>
-      </c>
       <c r="Q48" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="R48">
         <v>115</v>
@@ -4724,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="BC48" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE48" t="s">
         <v>100</v>
-      </c>
-      <c r="BE48" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:57" x14ac:dyDescent="0.3">
@@ -4738,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="E49" t="s">
         <v>59</v>
@@ -4750,19 +4702,19 @@
         <v>61</v>
       </c>
       <c r="H49" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I49">
         <v>2024</v>
       </c>
       <c r="J49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s">
         <v>10</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M49" t="s">
         <v>65</v>
@@ -4771,13 +4723,13 @@
         <v>66</v>
       </c>
       <c r="O49" t="s">
+        <v>97</v>
+      </c>
+      <c r="P49" t="s">
         <v>98</v>
       </c>
-      <c r="P49" t="s">
-        <v>99</v>
-      </c>
       <c r="Q49" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R49">
         <v>115</v>
@@ -4798,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="BC49" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE49" t="s">
         <v>100</v>
-      </c>
-      <c r="BE49" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:57" x14ac:dyDescent="0.3">
@@ -4812,7 +4764,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="E50" t="s">
         <v>59</v>
@@ -4824,19 +4776,19 @@
         <v>61</v>
       </c>
       <c r="H50" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I50">
         <v>2024</v>
       </c>
       <c r="J50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K50" t="s">
         <v>10</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M50" t="s">
         <v>65</v>
@@ -4845,13 +4797,13 @@
         <v>66</v>
       </c>
       <c r="O50" t="s">
+        <v>97</v>
+      </c>
+      <c r="P50" t="s">
         <v>98</v>
       </c>
-      <c r="P50" t="s">
-        <v>99</v>
-      </c>
       <c r="Q50" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R50">
         <v>115</v>
@@ -4872,10 +4824,10 @@
         <v>0</v>
       </c>
       <c r="BC50" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE50" t="s">
         <v>100</v>
-      </c>
-      <c r="BE50" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:57" x14ac:dyDescent="0.3">
@@ -4886,7 +4838,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="E51" t="s">
         <v>59</v>
@@ -4898,19 +4850,19 @@
         <v>61</v>
       </c>
       <c r="H51" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I51">
         <v>2024</v>
       </c>
       <c r="J51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s">
         <v>10</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M51" t="s">
         <v>65</v>
@@ -4919,13 +4871,13 @@
         <v>66</v>
       </c>
       <c r="O51" t="s">
+        <v>97</v>
+      </c>
+      <c r="P51" t="s">
         <v>98</v>
       </c>
-      <c r="P51" t="s">
-        <v>99</v>
-      </c>
       <c r="Q51" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R51">
         <v>115</v>
@@ -4946,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="BC51" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE51" t="s">
         <v>100</v>
-      </c>
-      <c r="BE51" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:57" x14ac:dyDescent="0.3">
@@ -4960,7 +4912,7 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="E52" t="s">
         <v>59</v>
@@ -4972,19 +4924,19 @@
         <v>61</v>
       </c>
       <c r="H52" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I52">
         <v>2024</v>
       </c>
       <c r="J52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s">
         <v>10</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M52" t="s">
         <v>65</v>
@@ -4993,13 +4945,13 @@
         <v>66</v>
       </c>
       <c r="O52" t="s">
+        <v>97</v>
+      </c>
+      <c r="P52" t="s">
         <v>98</v>
       </c>
-      <c r="P52" t="s">
-        <v>99</v>
-      </c>
       <c r="Q52" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R52">
         <v>115</v>
@@ -5020,10 +4972,10 @@
         <v>0</v>
       </c>
       <c r="BC52" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE52" t="s">
         <v>100</v>
-      </c>
-      <c r="BE52" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:57" x14ac:dyDescent="0.3">
@@ -5034,7 +4986,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
@@ -5046,19 +4998,19 @@
         <v>61</v>
       </c>
       <c r="H53" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I53">
         <v>2024</v>
       </c>
       <c r="J53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K53" t="s">
         <v>10</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M53" t="s">
         <v>65</v>
@@ -5067,13 +5019,13 @@
         <v>66</v>
       </c>
       <c r="O53" t="s">
+        <v>97</v>
+      </c>
+      <c r="P53" t="s">
         <v>98</v>
       </c>
-      <c r="P53" t="s">
-        <v>99</v>
-      </c>
       <c r="Q53" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R53">
         <v>115</v>
@@ -5094,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="BC53" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE53" t="s">
         <v>100</v>
-      </c>
-      <c r="BE53" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:57" x14ac:dyDescent="0.3">
@@ -5108,7 +5060,7 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="E54" t="s">
         <v>59</v>
@@ -5120,19 +5072,19 @@
         <v>61</v>
       </c>
       <c r="H54" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I54">
         <v>2024</v>
       </c>
       <c r="J54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K54" t="s">
         <v>10</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" t="s">
         <v>65</v>
@@ -5141,13 +5093,13 @@
         <v>66</v>
       </c>
       <c r="O54" t="s">
+        <v>97</v>
+      </c>
+      <c r="P54" t="s">
         <v>98</v>
       </c>
-      <c r="P54" t="s">
-        <v>99</v>
-      </c>
       <c r="Q54" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R54">
         <v>115</v>
@@ -5168,10 +5120,10 @@
         <v>0</v>
       </c>
       <c r="BC54" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE54" t="s">
         <v>100</v>
-      </c>
-      <c r="BE54" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:57" x14ac:dyDescent="0.3">
@@ -5182,7 +5134,7 @@
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="E55" t="s">
         <v>59</v>
@@ -5194,19 +5146,19 @@
         <v>61</v>
       </c>
       <c r="H55" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I55">
         <v>2024</v>
       </c>
       <c r="J55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K55" t="s">
         <v>10</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M55" t="s">
         <v>65</v>
@@ -5215,13 +5167,13 @@
         <v>66</v>
       </c>
       <c r="O55" t="s">
+        <v>97</v>
+      </c>
+      <c r="P55" t="s">
         <v>98</v>
       </c>
-      <c r="P55" t="s">
-        <v>99</v>
-      </c>
       <c r="Q55" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R55">
         <v>115</v>
@@ -5242,10 +5194,10 @@
         <v>0</v>
       </c>
       <c r="BC55" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE55" t="s">
         <v>100</v>
-      </c>
-      <c r="BE55" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:57" x14ac:dyDescent="0.3">
@@ -5256,7 +5208,7 @@
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
       <c r="E56" t="s">
         <v>59</v>
@@ -5268,19 +5220,19 @@
         <v>61</v>
       </c>
       <c r="H56" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I56">
         <v>2024</v>
       </c>
       <c r="J56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K56" t="s">
         <v>10</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M56" t="s">
         <v>65</v>
@@ -5289,13 +5241,13 @@
         <v>66</v>
       </c>
       <c r="O56" t="s">
+        <v>97</v>
+      </c>
+      <c r="P56" t="s">
         <v>98</v>
       </c>
-      <c r="P56" t="s">
-        <v>99</v>
-      </c>
       <c r="Q56" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R56">
         <v>115</v>
@@ -5316,10 +5268,10 @@
         <v>0</v>
       </c>
       <c r="BC56" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE56" t="s">
         <v>100</v>
-      </c>
-      <c r="BE56" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:57" x14ac:dyDescent="0.3">
@@ -5330,7 +5282,7 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="E57" t="s">
         <v>59</v>
@@ -5342,19 +5294,19 @@
         <v>61</v>
       </c>
       <c r="H57" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I57">
         <v>2024</v>
       </c>
       <c r="J57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s">
         <v>10</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M57" t="s">
         <v>65</v>
@@ -5363,13 +5315,13 @@
         <v>66</v>
       </c>
       <c r="O57" t="s">
+        <v>97</v>
+      </c>
+      <c r="P57" t="s">
         <v>98</v>
       </c>
-      <c r="P57" t="s">
-        <v>99</v>
-      </c>
       <c r="Q57" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R57">
         <v>115</v>
@@ -5390,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="BC57" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE57" t="s">
         <v>100</v>
-      </c>
-      <c r="BE57" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:57" x14ac:dyDescent="0.3">
@@ -5404,7 +5356,7 @@
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="E58" t="s">
         <v>59</v>
@@ -5416,19 +5368,19 @@
         <v>61</v>
       </c>
       <c r="H58" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I58">
         <v>2024</v>
       </c>
       <c r="J58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s">
         <v>10</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M58" t="s">
         <v>65</v>
@@ -5437,13 +5389,13 @@
         <v>66</v>
       </c>
       <c r="O58" t="s">
+        <v>97</v>
+      </c>
+      <c r="P58" t="s">
         <v>98</v>
       </c>
-      <c r="P58" t="s">
-        <v>99</v>
-      </c>
       <c r="Q58" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R58">
         <v>115</v>
@@ -5464,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="BC58" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE58" t="s">
         <v>100</v>
-      </c>
-      <c r="BE58" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:57" x14ac:dyDescent="0.3">
@@ -5478,7 +5430,7 @@
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="E59" t="s">
         <v>59</v>
@@ -5490,19 +5442,19 @@
         <v>61</v>
       </c>
       <c r="H59" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I59">
         <v>2024</v>
       </c>
       <c r="J59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K59" t="s">
         <v>10</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M59" t="s">
         <v>65</v>
@@ -5511,13 +5463,13 @@
         <v>66</v>
       </c>
       <c r="O59" t="s">
+        <v>97</v>
+      </c>
+      <c r="P59" t="s">
         <v>98</v>
       </c>
-      <c r="P59" t="s">
-        <v>99</v>
-      </c>
       <c r="Q59" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R59">
         <v>115</v>
@@ -5538,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="BC59" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE59" t="s">
         <v>100</v>
-      </c>
-      <c r="BE59" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:57" x14ac:dyDescent="0.3">
@@ -5552,7 +5504,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="E60" t="s">
         <v>59</v>
@@ -5564,19 +5516,19 @@
         <v>61</v>
       </c>
       <c r="H60" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I60">
         <v>2024</v>
       </c>
       <c r="J60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s">
         <v>10</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M60" t="s">
         <v>65</v>
@@ -5585,13 +5537,13 @@
         <v>66</v>
       </c>
       <c r="O60" t="s">
+        <v>97</v>
+      </c>
+      <c r="P60" t="s">
         <v>98</v>
       </c>
-      <c r="P60" t="s">
-        <v>99</v>
-      </c>
       <c r="Q60" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R60">
         <v>115</v>
@@ -5612,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="BC60" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE60" t="s">
         <v>100</v>
-      </c>
-      <c r="BE60" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:57" x14ac:dyDescent="0.3">
@@ -5626,7 +5578,7 @@
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="E61" t="s">
         <v>59</v>
@@ -5638,19 +5590,19 @@
         <v>61</v>
       </c>
       <c r="H61" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I61">
         <v>2024</v>
       </c>
       <c r="J61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K61" t="s">
         <v>10</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M61" t="s">
         <v>65</v>
@@ -5659,13 +5611,13 @@
         <v>66</v>
       </c>
       <c r="O61" t="s">
+        <v>97</v>
+      </c>
+      <c r="P61" t="s">
         <v>98</v>
       </c>
-      <c r="P61" t="s">
-        <v>99</v>
-      </c>
       <c r="Q61" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R61">
         <v>115</v>
@@ -5686,10 +5638,10 @@
         <v>0</v>
       </c>
       <c r="BC61" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE61" t="s">
         <v>100</v>
-      </c>
-      <c r="BE61" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:57" x14ac:dyDescent="0.3">
@@ -5700,7 +5652,7 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="E62" t="s">
         <v>59</v>
@@ -5712,19 +5664,19 @@
         <v>61</v>
       </c>
       <c r="H62" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="I62">
         <v>2024</v>
       </c>
       <c r="J62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K62" t="s">
         <v>10</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M62" t="s">
         <v>65</v>
@@ -5733,13 +5685,13 @@
         <v>66</v>
       </c>
       <c r="O62" t="s">
+        <v>97</v>
+      </c>
+      <c r="P62" t="s">
         <v>98</v>
       </c>
-      <c r="P62" t="s">
-        <v>99</v>
-      </c>
       <c r="Q62" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R62">
         <v>115</v>
@@ -5760,21 +5712,21 @@
         <v>0</v>
       </c>
       <c r="BC62" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE62" t="s">
         <v>100</v>
-      </c>
-      <c r="BE62" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
         <v>59</v>
@@ -5786,40 +5738,40 @@
         <v>61</v>
       </c>
       <c r="H63" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="I63">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J63" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K63" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="N63" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="O63" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="P63" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="Q63" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="R63">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="V63" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="W63" t="s">
         <v>71</v>
@@ -5828,27 +5780,30 @@
         <v>72</v>
       </c>
       <c r="BA63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB63">
         <v>0</v>
       </c>
       <c r="BC63" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>121</v>
       </c>
       <c r="BE63" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>59</v>
@@ -5860,69 +5815,63 @@
         <v>61</v>
       </c>
       <c r="H64" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I64">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J64" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="K64" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="s">
+        <v>65</v>
+      </c>
+      <c r="N64" t="s">
+        <v>127</v>
+      </c>
+      <c r="O64" t="s">
+        <v>128</v>
+      </c>
+      <c r="P64" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>130</v>
+      </c>
+      <c r="V64" t="s">
+        <v>91</v>
+      </c>
+      <c r="W64" t="s">
+        <v>71</v>
+      </c>
+      <c r="X64" t="s">
+        <v>72</v>
+      </c>
+      <c r="BA64">
         <v>1</v>
       </c>
-      <c r="M64" t="s">
-        <v>65</v>
-      </c>
-      <c r="N64" t="s">
-        <v>66</v>
-      </c>
-      <c r="O64" t="s">
-        <v>98</v>
-      </c>
-      <c r="P64" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>156</v>
-      </c>
-      <c r="R64">
-        <v>115</v>
-      </c>
-      <c r="V64" t="s">
-        <v>70</v>
-      </c>
-      <c r="W64" t="s">
-        <v>71</v>
-      </c>
-      <c r="X64" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA64">
-        <v>5</v>
-      </c>
       <c r="BB64">
         <v>0</v>
       </c>
       <c r="BC64" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE64" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="E65" t="s">
         <v>59</v>
@@ -5934,37 +5883,37 @@
         <v>61</v>
       </c>
       <c r="H65" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I65">
         <v>2024</v>
       </c>
       <c r="J65" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="K65" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="s">
         <v>65</v>
       </c>
       <c r="N65" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="O65" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="Q65" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="R65">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="V65" t="s">
         <v>70</v>
@@ -5976,27 +5925,27 @@
         <v>72</v>
       </c>
       <c r="BA65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB65">
         <v>0</v>
       </c>
       <c r="BC65" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE65" t="s">
-        <v>101</v>
+        <v>137</v>
+      </c>
+      <c r="BD65" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
         <v>59</v>
@@ -6008,37 +5957,37 @@
         <v>61</v>
       </c>
       <c r="H66" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="I66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J66" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="K66" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="N66" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="O66" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="P66" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="Q66" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="R66">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="V66" t="s">
         <v>70</v>
@@ -6050,27 +5999,30 @@
         <v>72</v>
       </c>
       <c r="BA66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB66">
         <v>0</v>
       </c>
       <c r="BC66" t="s">
-        <v>100</v>
+        <v>146</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>147</v>
       </c>
       <c r="BE66" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
         <v>59</v>
@@ -6082,69 +6034,72 @@
         <v>61</v>
       </c>
       <c r="H67" t="s">
+        <v>86</v>
+      </c>
+      <c r="I67">
+        <v>2026</v>
+      </c>
+      <c r="J67" t="s">
+        <v>151</v>
+      </c>
+      <c r="K67" t="s">
+        <v>64</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
+        <v>116</v>
+      </c>
+      <c r="N67" t="s">
+        <v>117</v>
+      </c>
+      <c r="O67" t="s">
+        <v>152</v>
+      </c>
+      <c r="P67" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>90</v>
+      </c>
+      <c r="R67">
+        <v>400</v>
+      </c>
+      <c r="V67" t="s">
+        <v>91</v>
+      </c>
+      <c r="W67" t="s">
+        <v>71</v>
+      </c>
+      <c r="X67" t="s">
+        <v>72</v>
+      </c>
+      <c r="BA67">
+        <v>2</v>
+      </c>
+      <c r="BB67">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="s">
+        <v>154</v>
+      </c>
+      <c r="BD67" t="s">
         <v>155</v>
       </c>
-      <c r="I67">
-        <v>2024</v>
-      </c>
-      <c r="J67" t="s">
-        <v>97</v>
-      </c>
-      <c r="K67" t="s">
-        <v>10</v>
-      </c>
-      <c r="L67">
-        <v>1</v>
-      </c>
-      <c r="M67" t="s">
-        <v>65</v>
-      </c>
-      <c r="N67" t="s">
-        <v>66</v>
-      </c>
-      <c r="O67" t="s">
-        <v>98</v>
-      </c>
-      <c r="P67" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q67" t="s">
+      <c r="BE67" t="s">
         <v>156</v>
-      </c>
-      <c r="R67">
-        <v>115</v>
-      </c>
-      <c r="V67" t="s">
-        <v>70</v>
-      </c>
-      <c r="W67" t="s">
-        <v>71</v>
-      </c>
-      <c r="X67" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA67">
-        <v>5</v>
-      </c>
-      <c r="BB67">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE67" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E68" t="s">
         <v>59</v>
@@ -6156,37 +6111,37 @@
         <v>61</v>
       </c>
       <c r="H68" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I68">
         <v>2024</v>
       </c>
       <c r="J68" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="K68" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="N68" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="O68" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="P68" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="Q68" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="R68">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="V68" t="s">
         <v>70</v>
@@ -6198,1052 +6153,13 @@
         <v>72</v>
       </c>
       <c r="BA68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB68">
         <v>0</v>
       </c>
       <c r="BC68" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE68" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69">
-        <v>4</v>
-      </c>
-      <c r="D69" t="s">
-        <v>176</v>
-      </c>
-      <c r="E69" t="s">
-        <v>59</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H69" t="s">
-        <v>62</v>
-      </c>
-      <c r="I69">
-        <v>2024</v>
-      </c>
-      <c r="J69" t="s">
-        <v>97</v>
-      </c>
-      <c r="K69" t="s">
-        <v>10</v>
-      </c>
-      <c r="L69">
-        <v>1</v>
-      </c>
-      <c r="M69" t="s">
-        <v>65</v>
-      </c>
-      <c r="N69" t="s">
-        <v>66</v>
-      </c>
-      <c r="O69" t="s">
-        <v>98</v>
-      </c>
-      <c r="P69" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>69</v>
-      </c>
-      <c r="R69">
-        <v>115</v>
-      </c>
-      <c r="V69" t="s">
-        <v>70</v>
-      </c>
-      <c r="W69" t="s">
-        <v>71</v>
-      </c>
-      <c r="X69" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA69">
-        <v>5</v>
-      </c>
-      <c r="BB69">
-        <v>0</v>
-      </c>
-      <c r="BC69" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE69" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="70" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70">
-        <v>4</v>
-      </c>
-      <c r="D70" t="s">
-        <v>177</v>
-      </c>
-      <c r="E70" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H70" t="s">
-        <v>62</v>
-      </c>
-      <c r="I70">
-        <v>2024</v>
-      </c>
-      <c r="J70" t="s">
-        <v>97</v>
-      </c>
-      <c r="K70" t="s">
-        <v>10</v>
-      </c>
-      <c r="L70">
-        <v>1</v>
-      </c>
-      <c r="M70" t="s">
-        <v>65</v>
-      </c>
-      <c r="N70" t="s">
-        <v>66</v>
-      </c>
-      <c r="O70" t="s">
-        <v>98</v>
-      </c>
-      <c r="P70" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>90</v>
-      </c>
-      <c r="R70">
-        <v>115</v>
-      </c>
-      <c r="V70" t="s">
-        <v>70</v>
-      </c>
-      <c r="W70" t="s">
-        <v>71</v>
-      </c>
-      <c r="X70" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA70">
-        <v>5</v>
-      </c>
-      <c r="BB70">
-        <v>0</v>
-      </c>
-      <c r="BC70" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE70" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="71" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>178</v>
-      </c>
-      <c r="E71" t="s">
-        <v>59</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H71" t="s">
-        <v>86</v>
-      </c>
-      <c r="I71">
-        <v>2024</v>
-      </c>
-      <c r="J71" t="s">
-        <v>97</v>
-      </c>
-      <c r="K71" t="s">
-        <v>10</v>
-      </c>
-      <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="M71" t="s">
-        <v>65</v>
-      </c>
-      <c r="N71" t="s">
-        <v>66</v>
-      </c>
-      <c r="O71" t="s">
-        <v>98</v>
-      </c>
-      <c r="P71" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>90</v>
-      </c>
-      <c r="R71">
-        <v>115</v>
-      </c>
-      <c r="V71" t="s">
-        <v>70</v>
-      </c>
-      <c r="W71" t="s">
-        <v>71</v>
-      </c>
-      <c r="X71" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA71">
-        <v>5</v>
-      </c>
-      <c r="BB71">
-        <v>0</v>
-      </c>
-      <c r="BC71" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE71" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72">
-        <v>4</v>
-      </c>
-      <c r="D72" t="s">
-        <v>179</v>
-      </c>
-      <c r="E72" t="s">
-        <v>59</v>
-      </c>
-      <c r="F72" t="s">
-        <v>60</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H72" t="s">
-        <v>86</v>
-      </c>
-      <c r="I72">
-        <v>2024</v>
-      </c>
-      <c r="J72" t="s">
-        <v>97</v>
-      </c>
-      <c r="K72" t="s">
-        <v>10</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72" t="s">
-        <v>65</v>
-      </c>
-      <c r="N72" t="s">
-        <v>66</v>
-      </c>
-      <c r="O72" t="s">
-        <v>98</v>
-      </c>
-      <c r="P72" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>90</v>
-      </c>
-      <c r="R72">
-        <v>115</v>
-      </c>
-      <c r="V72" t="s">
-        <v>70</v>
-      </c>
-      <c r="W72" t="s">
-        <v>71</v>
-      </c>
-      <c r="X72" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA72">
-        <v>5</v>
-      </c>
-      <c r="BB72">
-        <v>0</v>
-      </c>
-      <c r="BC72" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE72" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73">
-        <v>4</v>
-      </c>
-      <c r="D73" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H73" t="s">
-        <v>181</v>
-      </c>
-      <c r="I73">
-        <v>2024</v>
-      </c>
-      <c r="J73" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" t="s">
-        <v>10</v>
-      </c>
-      <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="M73" t="s">
-        <v>65</v>
-      </c>
-      <c r="N73" t="s">
-        <v>66</v>
-      </c>
-      <c r="O73" t="s">
-        <v>98</v>
-      </c>
-      <c r="P73" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>182</v>
-      </c>
-      <c r="R73">
-        <v>115</v>
-      </c>
-      <c r="V73" t="s">
-        <v>70</v>
-      </c>
-      <c r="W73" t="s">
-        <v>71</v>
-      </c>
-      <c r="X73" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA73">
-        <v>5</v>
-      </c>
-      <c r="BB73">
-        <v>0</v>
-      </c>
-      <c r="BC73" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE73" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="74" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>95</v>
-      </c>
-      <c r="C74">
-        <v>4</v>
-      </c>
-      <c r="D74" t="s">
-        <v>183</v>
-      </c>
-      <c r="E74" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74" t="s">
-        <v>60</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H74" t="s">
-        <v>140</v>
-      </c>
-      <c r="I74">
-        <v>2024</v>
-      </c>
-      <c r="J74" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" t="s">
-        <v>10</v>
-      </c>
-      <c r="L74">
-        <v>1</v>
-      </c>
-      <c r="M74" t="s">
-        <v>65</v>
-      </c>
-      <c r="N74" t="s">
-        <v>66</v>
-      </c>
-      <c r="O74" t="s">
-        <v>98</v>
-      </c>
-      <c r="P74" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>138</v>
-      </c>
-      <c r="R74">
-        <v>115</v>
-      </c>
-      <c r="V74" t="s">
-        <v>70</v>
-      </c>
-      <c r="W74" t="s">
-        <v>71</v>
-      </c>
-      <c r="X74" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA74">
-        <v>5</v>
-      </c>
-      <c r="BB74">
-        <v>0</v>
-      </c>
-      <c r="BC74" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE74" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75">
-        <v>4</v>
-      </c>
-      <c r="D75" t="s">
-        <v>184</v>
-      </c>
-      <c r="E75" t="s">
-        <v>59</v>
-      </c>
-      <c r="F75" t="s">
-        <v>60</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H75" t="s">
-        <v>144</v>
-      </c>
-      <c r="I75">
-        <v>2024</v>
-      </c>
-      <c r="J75" t="s">
-        <v>97</v>
-      </c>
-      <c r="K75" t="s">
-        <v>10</v>
-      </c>
-      <c r="L75">
-        <v>1</v>
-      </c>
-      <c r="M75" t="s">
-        <v>65</v>
-      </c>
-      <c r="N75" t="s">
-        <v>66</v>
-      </c>
-      <c r="O75" t="s">
-        <v>98</v>
-      </c>
-      <c r="P75" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>142</v>
-      </c>
-      <c r="R75">
-        <v>115</v>
-      </c>
-      <c r="V75" t="s">
-        <v>70</v>
-      </c>
-      <c r="W75" t="s">
-        <v>71</v>
-      </c>
-      <c r="X75" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA75">
-        <v>5</v>
-      </c>
-      <c r="BB75">
-        <v>0</v>
-      </c>
-      <c r="BC75" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE75" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76">
-        <v>4</v>
-      </c>
-      <c r="D76" t="s">
-        <v>185</v>
-      </c>
-      <c r="E76" t="s">
-        <v>59</v>
-      </c>
-      <c r="F76" t="s">
-        <v>60</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H76" t="s">
-        <v>144</v>
-      </c>
-      <c r="I76">
-        <v>2024</v>
-      </c>
-      <c r="J76" t="s">
-        <v>97</v>
-      </c>
-      <c r="K76" t="s">
-        <v>10</v>
-      </c>
-      <c r="L76">
-        <v>1</v>
-      </c>
-      <c r="M76" t="s">
-        <v>65</v>
-      </c>
-      <c r="N76" t="s">
-        <v>66</v>
-      </c>
-      <c r="O76" t="s">
-        <v>98</v>
-      </c>
-      <c r="P76" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>142</v>
-      </c>
-      <c r="R76">
-        <v>115</v>
-      </c>
-      <c r="V76" t="s">
-        <v>70</v>
-      </c>
-      <c r="W76" t="s">
-        <v>71</v>
-      </c>
-      <c r="X76" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA76">
-        <v>5</v>
-      </c>
-      <c r="BB76">
-        <v>0</v>
-      </c>
-      <c r="BC76" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE76" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>186</v>
-      </c>
-      <c r="C77">
-        <v>5</v>
-      </c>
-      <c r="D77" t="s">
-        <v>187</v>
-      </c>
-      <c r="E77" t="s">
-        <v>59</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H77" t="s">
-        <v>86</v>
-      </c>
-      <c r="I77">
-        <v>2023</v>
-      </c>
-      <c r="J77" t="s">
-        <v>188</v>
-      </c>
-      <c r="K77" t="s">
-        <v>64</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77" t="s">
-        <v>189</v>
-      </c>
-      <c r="N77" t="s">
-        <v>190</v>
-      </c>
-      <c r="O77" t="s">
-        <v>191</v>
-      </c>
-      <c r="P77" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>90</v>
-      </c>
-      <c r="R77">
-        <v>500</v>
-      </c>
-      <c r="V77" t="s">
-        <v>91</v>
-      </c>
-      <c r="W77" t="s">
-        <v>71</v>
-      </c>
-      <c r="X77" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA77">
-        <v>3</v>
-      </c>
-      <c r="BB77">
-        <v>0</v>
-      </c>
-      <c r="BC77" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD77" t="s">
-        <v>194</v>
-      </c>
-      <c r="BE77" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="78" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>196</v>
-      </c>
-      <c r="C78">
-        <v>6</v>
-      </c>
-      <c r="D78" t="s">
-        <v>197</v>
-      </c>
-      <c r="E78" t="s">
-        <v>59</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H78" t="s">
-        <v>198</v>
-      </c>
-      <c r="I78">
-        <v>2025</v>
-      </c>
-      <c r="J78" t="s">
-        <v>199</v>
-      </c>
-      <c r="K78" t="s">
-        <v>64</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78" t="s">
-        <v>65</v>
-      </c>
-      <c r="N78" t="s">
-        <v>200</v>
-      </c>
-      <c r="O78" t="s">
-        <v>201</v>
-      </c>
-      <c r="P78" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>203</v>
-      </c>
-      <c r="V78" t="s">
-        <v>91</v>
-      </c>
-      <c r="W78" t="s">
-        <v>71</v>
-      </c>
-      <c r="X78" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA78">
-        <v>1</v>
-      </c>
-      <c r="BB78">
-        <v>0</v>
-      </c>
-      <c r="BC78" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="79" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>205</v>
-      </c>
-      <c r="C79">
-        <v>7</v>
-      </c>
-      <c r="D79" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" t="s">
-        <v>60</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H79" t="s">
-        <v>198</v>
-      </c>
-      <c r="I79">
-        <v>2024</v>
-      </c>
-      <c r="J79" t="s">
-        <v>207</v>
-      </c>
-      <c r="K79" t="s">
-        <v>64</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79" t="s">
-        <v>65</v>
-      </c>
-      <c r="N79" t="s">
-        <v>200</v>
-      </c>
-      <c r="O79" t="s">
-        <v>208</v>
-      </c>
-      <c r="P79" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>203</v>
-      </c>
-      <c r="R79">
-        <v>500</v>
-      </c>
-      <c r="V79" t="s">
-        <v>70</v>
-      </c>
-      <c r="W79" t="s">
-        <v>71</v>
-      </c>
-      <c r="X79" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA79">
-        <v>3</v>
-      </c>
-      <c r="BB79">
-        <v>0</v>
-      </c>
-      <c r="BC79" t="s">
-        <v>210</v>
-      </c>
-      <c r="BD79" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="80" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80">
-        <v>8</v>
-      </c>
-      <c r="D80" t="s">
-        <v>213</v>
-      </c>
-      <c r="E80" t="s">
-        <v>59</v>
-      </c>
-      <c r="F80" t="s">
-        <v>60</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H80" t="s">
-        <v>151</v>
-      </c>
-      <c r="I80">
-        <v>2023</v>
-      </c>
-      <c r="J80" t="s">
-        <v>214</v>
-      </c>
-      <c r="K80" t="s">
-        <v>64</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80" t="s">
-        <v>215</v>
-      </c>
-      <c r="N80" t="s">
-        <v>216</v>
-      </c>
-      <c r="O80" t="s">
-        <v>217</v>
-      </c>
-      <c r="P80" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>152</v>
-      </c>
-      <c r="R80">
-        <v>240</v>
-      </c>
-      <c r="V80" t="s">
-        <v>70</v>
-      </c>
-      <c r="W80" t="s">
-        <v>71</v>
-      </c>
-      <c r="X80" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA80">
-        <v>4</v>
-      </c>
-      <c r="BB80">
-        <v>0</v>
-      </c>
-      <c r="BC80" t="s">
-        <v>219</v>
-      </c>
-      <c r="BD80" t="s">
-        <v>220</v>
-      </c>
-      <c r="BE80" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="81" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>222</v>
-      </c>
-      <c r="C81">
-        <v>9</v>
-      </c>
-      <c r="D81" t="s">
-        <v>223</v>
-      </c>
-      <c r="E81" t="s">
-        <v>59</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H81" t="s">
-        <v>86</v>
-      </c>
-      <c r="I81">
-        <v>2026</v>
-      </c>
-      <c r="J81" t="s">
-        <v>224</v>
-      </c>
-      <c r="K81" t="s">
-        <v>64</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81" t="s">
-        <v>189</v>
-      </c>
-      <c r="N81" t="s">
-        <v>190</v>
-      </c>
-      <c r="O81" t="s">
-        <v>225</v>
-      </c>
-      <c r="P81" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>90</v>
-      </c>
-      <c r="R81">
-        <v>400</v>
-      </c>
-      <c r="V81" t="s">
-        <v>91</v>
-      </c>
-      <c r="W81" t="s">
-        <v>71</v>
-      </c>
-      <c r="X81" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA81">
-        <v>2</v>
-      </c>
-      <c r="BB81">
-        <v>0</v>
-      </c>
-      <c r="BC81" t="s">
-        <v>227</v>
-      </c>
-      <c r="BD81" t="s">
-        <v>228</v>
-      </c>
-      <c r="BE81" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>230</v>
-      </c>
-      <c r="C82">
-        <v>10</v>
-      </c>
-      <c r="D82" t="s">
-        <v>231</v>
-      </c>
-      <c r="E82" t="s">
-        <v>59</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H82" t="s">
-        <v>198</v>
-      </c>
-      <c r="I82">
-        <v>2024</v>
-      </c>
-      <c r="J82" t="s">
-        <v>232</v>
-      </c>
-      <c r="K82" t="s">
-        <v>64</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82" t="s">
-        <v>215</v>
-      </c>
-      <c r="N82" t="s">
-        <v>233</v>
-      </c>
-      <c r="O82" t="s">
-        <v>234</v>
-      </c>
-      <c r="P82" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>203</v>
-      </c>
-      <c r="R82">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s">
-        <v>70</v>
-      </c>
-      <c r="W82" t="s">
-        <v>71</v>
-      </c>
-      <c r="X82" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA82">
-        <v>2</v>
-      </c>
-      <c r="BB82">
-        <v>0</v>
-      </c>
-      <c r="BC82" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/data/sources/countries/honduras.xlsx
+++ b/data/sources/countries/honduras.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión...</t>
+          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión...</t>
+          <t>Parque industrial textil y planta solar fotovoltaica de más de 300 MW en 400 hectáreas en Choloma, Cortés, con conexión.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Dam on the Rio del Hombre micro-basin in the Amarateca valley, under a letter of understanding signed on 12 September 2024 between CCECC and the mayor of Tegucigalpa, who valued it at USD 500-550M without specifying financing.</t>
+          <t>Dam on the Rio del Hombre micro-basin in the Amarateca valley, under a letter of understanding signed on 12 September.</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Expansion of the San Lorenzo and Puerto Cortes ports under a memorandum of understanding signed on 29 May 2023 between the National Port Authority and CHEC, structured in three phases and covered by a confidentiality clause.</t>
+          <t>Expansion of the San Lorenzo and Puerto Cortes ports under a memorandum of understanding signed on 29 May 2023 between.</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
